--- a/04_DESIGN_TABLES/DesignTable_5502_SW2.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_5502_SW2.xlsx
@@ -741,13 +741,13 @@
         <v>0.53</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.306</v>
+        <v>0.3055</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.306</v>
+        <v>0.3055</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.61199</v>
+        <v>0.61149</v>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
@@ -893,13 +893,13 @@
         <v>0.28</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.16166</v>
+        <v>0.16116</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.16166</v>
+        <v>0.16116</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.32332</v>
+        <v>0.32282</v>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
@@ -1045,13 +1045,13 @@
         <v>0.281</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.16224</v>
+        <v>0.16174</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.16224</v>
+        <v>0.16174</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.32447</v>
+        <v>0.32397</v>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
@@ -1197,13 +1197,13 @@
         <v>0.375</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.21651</v>
+        <v>0.21601</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.21651</v>
+        <v>0.21601</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.43301</v>
+        <v>0.43251</v>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
@@ -1349,13 +1349,13 @@
         <v>0.44</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.25403</v>
+        <v>0.25353</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.25403</v>
+        <v>0.25353</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.50807</v>
+        <v>0.50757</v>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
@@ -1501,13 +1501,13 @@
         <v>0.44</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.25403</v>
+        <v>0.25353</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.25403</v>
+        <v>0.25353</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.50807</v>
+        <v>0.50757</v>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
@@ -1653,13 +1653,13 @@
         <v>0.44</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.25403</v>
+        <v>0.25353</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.25403</v>
+        <v>0.25353</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.50807</v>
+        <v>0.50757</v>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
@@ -1805,13 +1805,13 @@
         <v>0.4375</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.25259</v>
+        <v>0.25209</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.25259</v>
+        <v>0.25209</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.50518</v>
+        <v>0.50468</v>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
@@ -1957,13 +1957,13 @@
         <v>0.4375</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.25259</v>
+        <v>0.25209</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.25259</v>
+        <v>0.25209</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.50518</v>
+        <v>0.50468</v>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
@@ -2109,13 +2109,13 @@
         <v>0.655</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.37816</v>
+        <v>0.37766</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.37816</v>
+        <v>0.37766</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.7563299999999999</v>
+        <v>0.75583</v>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
@@ -2261,13 +2261,13 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.54271</v>
+        <v>0.54221</v>
       </c>
       <c r="AI12" t="n">
-        <v>0.54271</v>
+        <v>0.54221</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.08542</v>
+        <v>1.08492</v>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
@@ -2418,13 +2418,13 @@
         <v>1.28</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.7390099999999999</v>
+        <v>0.73851</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.7390099999999999</v>
+        <v>0.73851</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.47802</v>
+        <v>1.47752</v>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
@@ -2575,13 +2575,13 @@
         <v>1.405</v>
       </c>
       <c r="AH14" t="n">
-        <v>0.81118</v>
+        <v>0.81068</v>
       </c>
       <c r="AI14" t="n">
-        <v>0.81118</v>
+        <v>0.81068</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.62235</v>
+        <v>1.62185</v>
       </c>
       <c r="AK14" t="inlineStr">
         <is>

--- a/04_DESIGN_TABLES/DesignTable_5502_SW2.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_5502_SW2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AS14"/>
+  <dimension ref="A1:AS21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -776,12 +776,17 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
           <t>Air-Way s128 only (double-pass 46 rows; page footer claimed 47); female NPTF per ANSI B1.20.3 | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); female legs: the forged hex arm stops 0.26 short of the port face and the end is a ROUND COLLAR of dia = the hex flats - MEASURED on the Brennan 2502-06-04-FG, 5502-04-04/-08-08/-16-16-FG, 5504-08-08-FG and 5605-08-08-08-FG STEPs (collar 0.260 at every size and leg; single manufacturer); port-mouth 45deg chamfer and hex chamfers not modelled; female NPTF legs: Air-Way tap drill to MS51503 P1 max (Brennan 5405-08-08 STEP: 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED -08 only)), tapered helix over P1; connecting drill to the axis crossing = the part's own D column (ASSUMPTION; capped at the tap drill where larger); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on W@REF=1.06~1.062; D@BORE=0.53~0.531</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -797,7 +802,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.89</v>
+        <v>0.78</v>
       </c>
       <c r="C3" t="n">
         <v>0.28</v>
@@ -824,7 +829,7 @@
         <v>0.19</v>
       </c>
       <c r="K3" t="n">
-        <v>0.89</v>
+        <v>0.78</v>
       </c>
       <c r="L3" t="n">
         <v>0.33</v>
@@ -854,7 +859,7 @@
         <v>0.16694</v>
       </c>
       <c r="U3" t="n">
-        <v>0.89</v>
+        <v>0.78</v>
       </c>
       <c r="V3" t="n">
         <v>0.33</v>
@@ -878,7 +883,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.51</v>
+        <v>0.4</v>
       </c>
       <c r="AD3" t="n">
         <v>0.5600000000000001</v>
@@ -933,7 +938,12 @@
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>Air-Way s128 only (double-pass 46 rows; page footer claimed 47); female NPTF per ANSI B1.20.3 | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); female legs: the forged hex arm stops 0.26 short of the port face and the end is a ROUND COLLAR of dia = the hex flats - MEASURED on the Brennan 2502-06-04-FG, 5502-04-04/-08-08/-16-16-FG, 5504-08-08-FG and 5605-08-08-08-FG STEPs (collar 0.260 at every size and leg; single manufacturer); port-mouth 45deg chamfer and hex chamfers not modelled; female NPTF legs: Air-Way tap drill to MS51503 P1 max (Brennan 5405-08-08 STEP: 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED -08 only)), tapered helix over P1; connecting drill to the axis crossing = the part's own D column (ASSUMPTION; capped at the tap drill where larger); each leg bore runs from its face to the axis crossing</t>
+          <t>Air-Way s128 only (double-pass 46 rows; page footer claimed 47); female NPTF per ANSI B1.20.3; N@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!N1458 = 0.780 (table had 0.89) [user 2026-10-18 A19] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); female legs: the forged hex arm stops 0.26 short of the port face and the end is a ROUND COLLAR of dia = the hex flats - MEASURED on the Brennan 2502-06-04-FG, 5502-04-04/-08-08/-16-16-FG, 5504-08-08-FG and 5605-08-08-08-FG STEPs (collar 0.260 at every size and leg; single manufacturer); port-mouth 45deg chamfer and hex chamfers not modelled; female NPTF legs: Air-Way tap drill to MS51503 P1 max (Brennan 5405-08-08 STEP: 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED -08 only)), tapered helix over P1; connecting drill to the axis crossing = the part's own D column (ASSUMPTION; capped at the tap drill where larger); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>A19 (user 2026-10-18, group 3 open): N@DRIVE 0.89 -&gt; OMi 0.780 (Items!N1458, M109)</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -945,122 +955,122 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>5502-04-02-FG</t>
+          <t>5502-02-04-FG</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.09</v>
+        <v>0.9</v>
       </c>
       <c r="C4" t="n">
-        <v>0.281</v>
+        <v>0.375</v>
       </c>
       <c r="D4" t="n">
-        <v>0.26092</v>
+        <v>0.19657</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4018</v>
+        <v>0.2639</v>
       </c>
       <c r="F4" t="n">
         <v>1.7899</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1582</v>
+        <v>0.1161</v>
       </c>
       <c r="H4" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.188</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="M4" t="n">
         <v>0.67</v>
       </c>
-      <c r="I4" t="n">
-        <v>0.281</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="K4" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0.46</v>
-      </c>
       <c r="N4" t="n">
-        <v>0.28</v>
+        <v>0.188</v>
       </c>
       <c r="O4" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.39314</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.2639</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.03704</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.19657</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.16694</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="W4" t="n">
         <v>0.67</v>
       </c>
-      <c r="P4" t="n">
-        <v>0.52183</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0.4018</v>
-      </c>
-      <c r="R4" t="n">
+      <c r="X4" t="n">
         <v>0.05556</v>
       </c>
-      <c r="S4" t="n">
-        <v>0.26092</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0.21647</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0.03704</v>
-      </c>
       <c r="Y4" t="n">
-        <v>0.165</v>
+        <v>0.215</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.19463</v>
+        <v>0.25944</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.67</v>
+        <v>0.88</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.75</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.53</v>
+        <v>0.52</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.75</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.41</v>
+        <v>0.62</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.281</v>
+        <v>0.375</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.281</v>
+        <v>0.375</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.16174</v>
+        <v>0.21601</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.16174</v>
+        <v>0.21601</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.32397</v>
+        <v>0.43251</v>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>5502-04-02-FG</t>
+          <t>5502-02-04-FG</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>90 deg Street Pipe Elbow, 1/4-18 NPTF x 1/8-27 NPTF (female)</t>
+          <t>90 deg Street Pipe Elbow, 1/8-27 NPTF x 1/4-18 NPTF (female)</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
@@ -1070,12 +1080,12 @@
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>1/4-18 NPTF</t>
+          <t>1/8-27 NPTF</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>1/8-27 NPTF (female)</t>
+          <t>1/4-18 NPTF (female)</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
@@ -1085,26 +1095,31 @@
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>Air-Way s128 only (double-pass 46 rows; page footer claimed 47); female NPTF per ANSI B1.20.3; W@REF: OMi WebsitePartsInfo2026.xlsx Items!R1461 Hex Flat = 0.562 (table had 0.75) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); female legs: the forged hex arm stops 0.26 short of the port face and the end is a ROUND COLLAR of dia = the hex flats - MEASURED on the Brennan 2502-06-04-FG, 5502-04-04/-08-08/-16-16-FG, 5504-08-08-FG and 5605-08-08-08-FG STEPs (collar 0.260 at every size and leg; single manufacturer); port-mouth 45deg chamfer and hex chamfers not modelled; female NPTF legs: Air-Way tap drill to MS51503 P1 max (Brennan 5405-08-08 STEP: 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED -08 only)), tapered helix over P1; connecting drill to the axis crossing = the part's own D column (ASSUMPTION; capped at the tap drill where larger); each leg bore runs from its face to the axis crossing</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 5502-02-04 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): N@DRIVE: Brennan TFA catalog p.31 table TFA-p031-t03 "5502-FG MP-FP 90 DEG ELBOW STREET ELBOW" row 5502-02-04-FG col "N LGTH" = "0.900" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 457.2, page verified True) [Brennan = yes 2026-10-18] - axis crossing to the male NPTF tip (column mapping: REPORT.md, table 5502); = OMi WebsitePartsInfo2026 Items!N1459 "M 1 Size" = 0.900 (same value; OMi and Brennan count as one source); N1@DRIVE: Brennan TFA catalog p.31 table TFA-p031-t03 "5502-FG MP-FP 90 DEG ELBOW STREET ELBOW" row 5502-02-04-FG col "N1 LGTH" = "0.880" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 457.2, page verified True) [Brennan = yes 2026-10-18] - axis crossing to the female NPTF port face (column mapping: REPORT.md, table 5502); = OMi WebsitePartsInfo2026 Items!P1459 "L 1 Size" = 0.880 (same value; OMi and Brennan count as one source); W@REF: Brennan TFA catalog p.31 table TFA-p031-t03 "5502-FG MP-FP 90 DEG ELBOW STREET ELBOW" row 5502-02-04-FG col "Y FLATS" = "0.750" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 457.2, page verified True) [Brennan = yes 2026-10-18] - forged body flats (column mapping: REPORT.md, table 5502); = OMi WebsitePartsInfo2026 Items!R1459 "Hex Flat" = 0.750 (same value; OMi and Brennan count as one source); D@BORE: Brennan TFA catalog p.31 table TFA-p031-t03 "5502-FG MP-FP 90 DEG ELBOW STREET ELBOW" row 5502-02-04-FG col "A1 DRILL" = "0.188" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 457.2, page verified True) [Brennan = yes 2026-10-18] - male end drill (column mapping: REPORT.md, table 5502); = OMi WebsitePartsInfo2026 Items!S1459 "Side 1 ID" = 0.188 (same value; OMi and Brennan count as one source); TAPDRILL@BORE: end library: tap drill of the -04 female NPTF port = 0.43 (gen_straight2 FPT[4] = templates/DesignTable_2405_SW2.xlsx TAPDRILL@BORE_A; = Air-Way's per-size tap drill of OPEN_QUESTIONS A1) [Q-TRANSFER-TAPDRILL = A1 answered YES 2026-10-18 (00_DOCS/ANSWERS_2026-10-18.md): Air-Way per-size tap drill on existing families]; THDMAJ_A1@DRIVE: end library: pipe OD of the -02 NPTF thread = 0.405 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[2], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_A2@DRIVE: end library: pipe OD of the -04 NPTF thread = 0.54 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[4], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; $PRP@Threads: thread callouts from the part number dashes in the format of the table's other rows; = Brennan TFA-p031-t03 thread columns (A1 NPTF 1/8-27, A2 NPTF 1/4-18) and OMi Items Side 1 / 2 / 3 Thread | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); female legs: the forged hex arm stops 0.26 short of the port face and the end is a ROUND COLLAR of dia = the hex flats - MEASURED on the Brennan 2502-06-04-FG, 5502-04-04/-08-08/-16-16-FG, 5504-08-08-FG and 5605-08-08-08-FG STEPs (collar 0.260 at every size and leg; single manufacturer); port-mouth 45deg chamfer and hex chamfers not modelled; female NPTF legs: Air-Way tap drill to MS51503 P1 max (Brennan 5405-08-08 STEP: 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED -08 only)), tapered helix over P1; connecting drill to the axis crossing = the part's own D column (ASSUMPTION; capped at the tap drill where larger); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 5502-02-04 dims are NOT assumed; confirm before modelling | 2026-10-18 Brennan = yes (wave2 tee_elbow, staged, not shipped): sizes from the Brennan TFA catalog (= OMi Items, one source), end details from the end library; marked $PRP@DimSource BRENNAN (to undo: clear the BRENNAN cells, set the row MISSING, regenerate)</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>5502-04-02-FG</t>
+          <t>5502-02-04-FG</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5502-04-04-FG</t>
+          <t>5502-04-02-FG</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>1.09</v>
       </c>
       <c r="C5" t="n">
-        <v>0.375</v>
+        <v>0.281</v>
       </c>
       <c r="D5" t="n">
         <v>0.26092</v>
@@ -1119,10 +1134,10 @@
         <v>0.1582</v>
       </c>
       <c r="H5" t="n">
-        <v>0.88</v>
+        <v>0.67</v>
       </c>
       <c r="I5" t="n">
-        <v>0.375</v>
+        <v>0.281</v>
       </c>
       <c r="J5" t="n">
         <v>0.28</v>
@@ -1131,16 +1146,16 @@
         <v>1.09</v>
       </c>
       <c r="L5" t="n">
-        <v>0.43</v>
+        <v>0.33</v>
       </c>
       <c r="M5" t="n">
-        <v>0.67</v>
+        <v>0.46</v>
       </c>
       <c r="N5" t="n">
         <v>0.28</v>
       </c>
       <c r="O5" t="n">
-        <v>0.88</v>
+        <v>0.67</v>
       </c>
       <c r="P5" t="n">
         <v>0.52183</v>
@@ -1161,58 +1176,58 @@
         <v>1.09</v>
       </c>
       <c r="V5" t="n">
-        <v>0.43</v>
+        <v>0.33</v>
       </c>
       <c r="W5" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.03704</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0.165</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0.19463</v>
+      </c>
+      <c r="AA5" t="n">
         <v>0.67</v>
       </c>
-      <c r="X5" t="n">
-        <v>0.05556</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0.215</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>0.25944</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>0.88</v>
-      </c>
       <c r="AB5" t="n">
-        <v>0.75</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="AC5" t="n">
         <v>0.53</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.75</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.62</v>
+        <v>0.41</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.375</v>
+        <v>0.281</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.375</v>
+        <v>0.281</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.21601</v>
+        <v>0.16174</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.21601</v>
+        <v>0.16174</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.43251</v>
+        <v>0.32397</v>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>5502-04-04-FG</t>
+          <t>5502-04-02-FG</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>90 deg Street Pipe Elbow, 1/4-18 NPTF x 1/4-18 NPTF (female)</t>
+          <t>90 deg Street Pipe Elbow, 1/4-18 NPTF x 1/8-27 NPTF (female)</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
@@ -1227,7 +1242,7 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>1/4-18 NPTF (female)</t>
+          <t>1/8-27 NPTF (female)</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
@@ -1237,26 +1252,26 @@
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>Air-Way s128 only (double-pass 46 rows; page footer claimed 47); female NPTF per ANSI B1.20.3 | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); female legs: the forged hex arm stops 0.26 short of the port face and the end is a ROUND COLLAR of dia = the hex flats - MEASURED on the Brennan 2502-06-04-FG, 5502-04-04/-08-08/-16-16-FG, 5504-08-08-FG and 5605-08-08-08-FG STEPs (collar 0.260 at every size and leg; single manufacturer); port-mouth 45deg chamfer and hex chamfers not modelled; female NPTF legs: Air-Way tap drill to MS51503 P1 max (Brennan 5405-08-08 STEP: 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED -08 only)), tapered helix over P1; connecting drill to the axis crossing = the part's own D column (ASSUMPTION; capped at the tap drill where larger); each leg bore runs from its face to the axis crossing</t>
+          <t>Air-Way s128 only (double-pass 46 rows; page footer claimed 47); female NPTF per ANSI B1.20.3; W@REF: OMi WebsitePartsInfo2026.xlsx Items!R1461 Hex Flat = 0.562 (table had 0.75) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); female legs: the forged hex arm stops 0.26 short of the port face and the end is a ROUND COLLAR of dia = the hex flats - MEASURED on the Brennan 2502-06-04-FG, 5502-04-04/-08-08/-16-16-FG, 5504-08-08-FG and 5605-08-08-08-FG STEPs (collar 0.260 at every size and leg; single manufacturer); port-mouth 45deg chamfer and hex chamfers not modelled; female NPTF legs: Air-Way tap drill to MS51503 P1 max (Brennan 5405-08-08 STEP: 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED -08 only)), tapered helix over P1; connecting drill to the axis crossing = the part's own D column (ASSUMPTION; capped at the tap drill where larger); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>5502-04-04-FG</t>
+          <t>5502-04-02-FG</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>5502-04-06-FG</t>
+          <t>5502-04-04-FG</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.22</v>
+        <v>1.09</v>
       </c>
       <c r="C6" t="n">
-        <v>0.44</v>
+        <v>0.375</v>
       </c>
       <c r="D6" t="n">
         <v>0.26092</v>
@@ -1271,28 +1286,28 @@
         <v>0.1582</v>
       </c>
       <c r="H6" t="n">
-        <v>1.02</v>
+        <v>0.88</v>
       </c>
       <c r="I6" t="n">
-        <v>0.44</v>
+        <v>0.375</v>
       </c>
       <c r="J6" t="n">
         <v>0.28</v>
       </c>
       <c r="K6" t="n">
-        <v>1.22</v>
+        <v>1.09</v>
       </c>
       <c r="L6" t="n">
-        <v>0.57</v>
+        <v>0.43</v>
       </c>
       <c r="M6" t="n">
-        <v>0.68</v>
+        <v>0.67</v>
       </c>
       <c r="N6" t="n">
         <v>0.28</v>
       </c>
       <c r="O6" t="n">
-        <v>1.02</v>
+        <v>0.88</v>
       </c>
       <c r="P6" t="n">
         <v>0.52183</v>
@@ -1310,61 +1325,61 @@
         <v>0.21647</v>
       </c>
       <c r="U6" t="n">
-        <v>1.22</v>
+        <v>1.09</v>
       </c>
       <c r="V6" t="n">
-        <v>0.57</v>
+        <v>0.43</v>
       </c>
       <c r="W6" t="n">
-        <v>0.68</v>
+        <v>0.67</v>
       </c>
       <c r="X6" t="n">
         <v>0.05556</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.285</v>
+        <v>0.215</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.32944</v>
+        <v>0.25944</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.02</v>
+        <v>0.88</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.88</v>
+        <v>0.75</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.66</v>
+        <v>0.53</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.88</v>
+        <v>0.75</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.76</v>
+        <v>0.62</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.44</v>
+        <v>0.375</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.44</v>
+        <v>0.375</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.25353</v>
+        <v>0.21601</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.25353</v>
+        <v>0.21601</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.50757</v>
+        <v>0.43251</v>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>5502-04-06-FG</t>
+          <t>5502-04-04-FG</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>90 deg Street Pipe Elbow, 1/4-18 NPTF x 3/8-18 NPTF (female)</t>
+          <t>90 deg Street Pipe Elbow, 1/4-18 NPTF x 1/4-18 NPTF (female)</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
@@ -1379,12 +1394,12 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>3/8-18 NPTF (female)</t>
+          <t>1/4-18 NPTF (female)</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
@@ -1392,16 +1407,21 @@
           <t>Air-Way s128 only (double-pass 46 rows; page footer claimed 47); female NPTF per ANSI B1.20.3 | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); female legs: the forged hex arm stops 0.26 short of the port face and the end is a ROUND COLLAR of dia = the hex flats - MEASURED on the Brennan 2502-06-04-FG, 5502-04-04/-08-08/-16-16-FG, 5504-08-08-FG and 5605-08-08-08-FG STEPs (collar 0.260 at every size and leg; single manufacturer); port-mouth 45deg chamfer and hex chamfers not modelled; female NPTF legs: Air-Way tap drill to MS51503 P1 max (Brennan 5405-08-08 STEP: 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED -08 only)), tapered helix over P1; connecting drill to the axis crossing = the part's own D column (ASSUMPTION; capped at the tap drill where larger); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on W@REF=0.75~0.750; D@BORE=0.28~0.281</t>
+        </is>
+      </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>5502-04-06-FG</t>
+          <t>5502-04-04-FG</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5502-06-04-FG</t>
+          <t>5502-04-06-FG</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -1411,76 +1431,76 @@
         <v>0.44</v>
       </c>
       <c r="D7" t="n">
-        <v>0.32823</v>
+        <v>0.26092</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4078</v>
+        <v>0.4018</v>
       </c>
       <c r="F7" t="n">
         <v>1.7899</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1522</v>
+        <v>0.1582</v>
       </c>
       <c r="H7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I7" t="n">
         <v>0.44</v>
       </c>
       <c r="J7" t="n">
-        <v>0.41</v>
+        <v>0.28</v>
       </c>
       <c r="K7" t="n">
         <v>1.22</v>
       </c>
       <c r="L7" t="n">
-        <v>0.43</v>
+        <v>0.57</v>
       </c>
       <c r="M7" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="N7" t="n">
-        <v>0.41</v>
+        <v>0.28</v>
       </c>
       <c r="O7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P7" t="n">
-        <v>0.65645</v>
+        <v>0.52183</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.4078</v>
+        <v>0.4018</v>
       </c>
       <c r="R7" t="n">
         <v>0.05556</v>
       </c>
       <c r="S7" t="n">
-        <v>0.32823</v>
+        <v>0.26092</v>
       </c>
       <c r="T7" t="n">
-        <v>0.28378</v>
+        <v>0.21647</v>
       </c>
       <c r="U7" t="n">
         <v>1.22</v>
       </c>
       <c r="V7" t="n">
-        <v>0.43</v>
+        <v>0.57</v>
       </c>
       <c r="W7" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="X7" t="n">
         <v>0.05556</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.215</v>
+        <v>0.285</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.25944</v>
+        <v>0.32944</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AB7" t="n">
         <v>0.88</v>
@@ -1492,7 +1512,7 @@
         <v>0.88</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="AF7" t="n">
         <v>0.44</v>
@@ -1511,12 +1531,12 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>5502-06-04-FG</t>
+          <t>5502-04-06-FG</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>90 deg Street Pipe Elbow, 3/8-18 NPTF x 1/4-18 NPTF (female)</t>
+          <t>90 deg Street Pipe Elbow, 1/4-18 NPTF x 3/8-18 NPTF (female)</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -1526,17 +1546,17 @@
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>3/8-18 NPTF</t>
+          <t>1/4-18 NPTF</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>1/4-18 NPTF (female)</t>
+          <t>3/8-18 NPTF (female)</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
@@ -1544,16 +1564,21 @@
           <t>Air-Way s128 only (double-pass 46 rows; page footer claimed 47); female NPTF per ANSI B1.20.3 | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); female legs: the forged hex arm stops 0.26 short of the port face and the end is a ROUND COLLAR of dia = the hex flats - MEASURED on the Brennan 2502-06-04-FG, 5502-04-04/-08-08/-16-16-FG, 5504-08-08-FG and 5605-08-08-08-FG STEPs (collar 0.260 at every size and leg; single manufacturer); port-mouth 45deg chamfer and hex chamfers not modelled; female NPTF legs: Air-Way tap drill to MS51503 P1 max (Brennan 5405-08-08 STEP: 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED -08 only)), tapered helix over P1; connecting drill to the axis crossing = the part's own D column (ASSUMPTION; capped at the tap drill where larger); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on W@REF=0.88~0.875; D@BORE=0.28~0.281</t>
+        </is>
+      </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>5502-06-04-FG</t>
+          <t>5502-04-06-FG</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>5502-06-06-FG</t>
+          <t>5502-06-04-FG</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -1575,7 +1600,7 @@
         <v>0.1522</v>
       </c>
       <c r="H8" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="I8" t="n">
         <v>0.44</v>
@@ -1587,16 +1612,16 @@
         <v>1.22</v>
       </c>
       <c r="L8" t="n">
-        <v>0.57</v>
+        <v>0.43</v>
       </c>
       <c r="M8" t="n">
-        <v>0.68</v>
+        <v>0.67</v>
       </c>
       <c r="N8" t="n">
         <v>0.41</v>
       </c>
       <c r="O8" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="P8" t="n">
         <v>0.65645</v>
@@ -1617,22 +1642,22 @@
         <v>1.22</v>
       </c>
       <c r="V8" t="n">
-        <v>0.57</v>
+        <v>0.43</v>
       </c>
       <c r="W8" t="n">
-        <v>0.68</v>
+        <v>0.67</v>
       </c>
       <c r="X8" t="n">
         <v>0.05556</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.285</v>
+        <v>0.215</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.32944</v>
+        <v>0.25944</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AB8" t="n">
         <v>0.88</v>
@@ -1644,7 +1669,7 @@
         <v>0.88</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.76</v>
+        <v>0.75</v>
       </c>
       <c r="AF8" t="n">
         <v>0.44</v>
@@ -1663,12 +1688,12 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>5502-06-06-FG</t>
+          <t>5502-06-04-FG</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>90 deg Street Pipe Elbow, 3/8-18 NPTF x 3/8-18 NPTF (female)</t>
+          <t>90 deg Street Pipe Elbow, 3/8-18 NPTF x 1/4-18 NPTF (female)</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
@@ -1683,12 +1708,12 @@
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>3/8-18 NPTF (female)</t>
+          <t>1/4-18 NPTF (female)</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
@@ -1696,131 +1721,136 @@
           <t>Air-Way s128 only (double-pass 46 rows; page footer claimed 47); female NPTF per ANSI B1.20.3 | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); female legs: the forged hex arm stops 0.26 short of the port face and the end is a ROUND COLLAR of dia = the hex flats - MEASURED on the Brennan 2502-06-04-FG, 5502-04-04/-08-08/-16-16-FG, 5504-08-08-FG and 5605-08-08-08-FG STEPs (collar 0.260 at every size and leg; single manufacturer); port-mouth 45deg chamfer and hex chamfers not modelled; female NPTF legs: Air-Way tap drill to MS51503 P1 max (Brennan 5405-08-08 STEP: 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED -08 only)), tapered helix over P1; connecting drill to the axis crossing = the part's own D column (ASSUMPTION; capped at the tap drill where larger); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on W@REF=0.88~0.875; D@BORE=0.41~0.406</t>
+        </is>
+      </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>5502-06-06-FG</t>
+          <t>5502-06-04-FG</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>5502-08-04-FG</t>
+          <t>5502-06-06-FG</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.47</v>
+        <v>1.22</v>
       </c>
       <c r="C9" t="n">
-        <v>0.4375</v>
+        <v>0.44</v>
       </c>
       <c r="D9" t="n">
-        <v>0.40779</v>
+        <v>0.32823</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5337</v>
+        <v>0.4078</v>
       </c>
       <c r="F9" t="n">
         <v>1.7899</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2163</v>
+        <v>0.1522</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4375</v>
+        <v>0.44</v>
       </c>
       <c r="J9" t="n">
-        <v>0.53</v>
+        <v>0.41</v>
       </c>
       <c r="K9" t="n">
-        <v>1.47</v>
+        <v>1.22</v>
       </c>
       <c r="L9" t="n">
-        <v>0.43</v>
+        <v>0.57</v>
       </c>
       <c r="M9" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="N9" t="n">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
       <c r="O9" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="P9" t="n">
-        <v>0.81557</v>
+        <v>0.65645</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.5337</v>
+        <v>0.4078</v>
       </c>
       <c r="R9" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.05556</v>
       </c>
       <c r="S9" t="n">
-        <v>0.40779</v>
+        <v>0.32823</v>
       </c>
       <c r="T9" t="n">
-        <v>0.35064</v>
+        <v>0.28378</v>
       </c>
       <c r="U9" t="n">
-        <v>1.47</v>
+        <v>1.22</v>
       </c>
       <c r="V9" t="n">
-        <v>0.43</v>
+        <v>0.57</v>
       </c>
       <c r="W9" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="X9" t="n">
         <v>0.05556</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.215</v>
+        <v>0.285</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.25944</v>
+        <v>0.32944</v>
       </c>
       <c r="AA9" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.875</v>
+        <v>0.88</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.72</v>
+        <v>0.66</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.875</v>
+        <v>0.88</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.74</v>
+        <v>0.76</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.4375</v>
+        <v>0.44</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.4375</v>
+        <v>0.44</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.25209</v>
+        <v>0.25353</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.25209</v>
+        <v>0.25353</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.50468</v>
+        <v>0.50757</v>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>5502-08-04-FG</t>
+          <t>5502-06-06-FG</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>90 deg Street Pipe Elbow, 1/2-14 NPTF x 1/4-18 NPTF (female)</t>
+          <t>90 deg Street Pipe Elbow, 3/8-18 NPTF x 3/8-18 NPTF (female)</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
@@ -1830,149 +1860,154 @@
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>1/2-14 NPTF</t>
+          <t>3/8-18 NPTF</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>1/4-18 NPTF (female)</t>
+          <t>3/8-18 NPTF (female)</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>Air-Way s128 only (double-pass 46 rows; page footer claimed 47); female NPTF per ANSI B1.20.3; W@REF: OMi WebsitePartsInfo2026.xlsx Items!R1469 Hex Flat = 0.875 (table had 1.06) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); female legs: the forged hex arm stops 0.26 short of the port face and the end is a ROUND COLLAR of dia = the hex flats - MEASURED on the Brennan 2502-06-04-FG, 5502-04-04/-08-08/-16-16-FG, 5504-08-08-FG and 5605-08-08-08-FG STEPs (collar 0.260 at every size and leg; single manufacturer); port-mouth 45deg chamfer and hex chamfers not modelled; female NPTF legs: Air-Way tap drill to MS51503 P1 max (Brennan 5405-08-08 STEP: 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED -08 only)), tapered helix over P1; connecting drill to the axis crossing = the part's own D column (ASSUMPTION; capped at the tap drill where larger); each leg bore runs from its face to the axis crossing</t>
+          <t>Air-Way s128 only (double-pass 46 rows; page footer claimed 47); female NPTF per ANSI B1.20.3 | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); female legs: the forged hex arm stops 0.26 short of the port face and the end is a ROUND COLLAR of dia = the hex flats - MEASURED on the Brennan 2502-06-04-FG, 5502-04-04/-08-08/-16-16-FG, 5504-08-08-FG and 5605-08-08-08-FG STEPs (collar 0.260 at every size and leg; single manufacturer); port-mouth 45deg chamfer and hex chamfers not modelled; female NPTF legs: Air-Way tap drill to MS51503 P1 max (Brennan 5405-08-08 STEP: 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED -08 only)), tapered helix over P1; connecting drill to the axis crossing = the part's own D column (ASSUMPTION; capped at the tap drill where larger); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on W@REF=0.88~0.875; D@BORE=0.41~0.406</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>5502-08-04-FG</t>
+          <t>5502-06-06-FG</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>5502-08-06-FG</t>
+          <t>5502-06-08-FG</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.47</v>
+        <v>1.28</v>
       </c>
       <c r="C10" t="n">
-        <v>0.4375</v>
+        <v>0.531</v>
       </c>
       <c r="D10" t="n">
-        <v>0.40779</v>
+        <v>0.32823</v>
       </c>
       <c r="E10" t="n">
-        <v>0.5337</v>
+        <v>0.4078</v>
       </c>
       <c r="F10" t="n">
         <v>1.7899</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2163</v>
+        <v>0.1522</v>
       </c>
       <c r="H10" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="I10" t="n">
-        <v>0.4375</v>
+        <v>0.531</v>
       </c>
       <c r="J10" t="n">
-        <v>0.53</v>
+        <v>0.406</v>
       </c>
       <c r="K10" t="n">
-        <v>1.47</v>
+        <v>1.28</v>
       </c>
       <c r="L10" t="n">
-        <v>0.57</v>
+        <v>0.7</v>
       </c>
       <c r="M10" t="n">
-        <v>0.68</v>
+        <v>0.9</v>
       </c>
       <c r="N10" t="n">
-        <v>0.53</v>
+        <v>0.406</v>
       </c>
       <c r="O10" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="P10" t="n">
-        <v>0.81557</v>
+        <v>0.65645</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.5337</v>
+        <v>0.4078</v>
       </c>
       <c r="R10" t="n">
+        <v>0.05556</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.28378</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="X10" t="n">
         <v>0.07142999999999999</v>
       </c>
-      <c r="S10" t="n">
-        <v>0.40779</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0.35064</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0.05556</v>
-      </c>
       <c r="Y10" t="n">
-        <v>0.285</v>
+        <v>0.35</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.32944</v>
+        <v>0.40714</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.875</v>
+        <v>1.062</v>
       </c>
       <c r="AC10" t="n">
         <v>0.72</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.875</v>
+        <v>1.062</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.75</v>
+        <v>0.97</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.4375</v>
+        <v>0.531</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.4375</v>
+        <v>0.531</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.25209</v>
+        <v>0.30607</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.25209</v>
+        <v>0.30607</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.50468</v>
+        <v>0.61265</v>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>5502-08-06-FG</t>
+          <t>5502-06-08-FG</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>90 deg Street Pipe Elbow, 1/2-14 NPTF x 3/8-18 NPTF (female)</t>
+          <t>90 deg Street Pipe Elbow, 3/8-18 NPTF x 1/2-14 NPTF (female)</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -1982,12 +2017,12 @@
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>1/2-14 NPTF</t>
+          <t>3/8-18 NPTF</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>3/8-18 NPTF (female)</t>
+          <t>1/2-14 NPTF (female)</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
@@ -1997,26 +2032,31 @@
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>Air-Way s128 only (double-pass 46 rows; page footer claimed 47); female NPTF per ANSI B1.20.3; W@REF: OMi WebsitePartsInfo2026.xlsx Items!R1470 Hex Flat = 0.875 (table had 1.06) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); female legs: the forged hex arm stops 0.26 short of the port face and the end is a ROUND COLLAR of dia = the hex flats - MEASURED on the Brennan 2502-06-04-FG, 5502-04-04/-08-08/-16-16-FG, 5504-08-08-FG and 5605-08-08-08-FG STEPs (collar 0.260 at every size and leg; single manufacturer); port-mouth 45deg chamfer and hex chamfers not modelled; female NPTF legs: Air-Way tap drill to MS51503 P1 max (Brennan 5405-08-08 STEP: 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED -08 only)), tapered helix over P1; connecting drill to the axis crossing = the part's own D column (ASSUMPTION; capped at the tap drill where larger); each leg bore runs from its face to the axis crossing</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 5502-06-08 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): N@DRIVE: Brennan TFA catalog p.31 table TFA-p031-t03 "5502-FG MP-FP 90 DEG ELBOW STREET ELBOW" row 5502-06-08-FG col "N LGTH" = "1.280" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 527.8, page verified True) [Brennan = yes 2026-10-18] - axis crossing to the male NPTF tip (column mapping: REPORT.md, table 5502); = OMi WebsitePartsInfo2026 Items!N1468 "M 1 Size" = 1.280 (same value; OMi and Brennan count as one source); N1@DRIVE: Brennan TFA catalog p.31 table TFA-p031-t03 "5502-FG MP-FP 90 DEG ELBOW STREET ELBOW" row 5502-06-08-FG col "N1 LGTH" = "1.230" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 527.8, page verified True) [Brennan = yes 2026-10-18] - axis crossing to the female NPTF port face (column mapping: REPORT.md, table 5502); = OMi WebsitePartsInfo2026 Items!P1468 "L 1 Size" = 1.230 (same value; OMi and Brennan count as one source); W@REF: Brennan TFA catalog p.31 table TFA-p031-t03 "5502-FG MP-FP 90 DEG ELBOW STREET ELBOW" row 5502-06-08-FG col "Y FLATS" = "1.062" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 527.8, page verified True) [Brennan = yes 2026-10-18] - forged body flats (column mapping: REPORT.md, table 5502); = OMi WebsitePartsInfo2026 Items!R1468 "Hex Flat" = 1.062 (same value; OMi and Brennan count as one source); D@BORE: Brennan TFA catalog p.31 table TFA-p031-t03 "5502-FG MP-FP 90 DEG ELBOW STREET ELBOW" row 5502-06-08-FG col "A1 DRILL" = "0.406" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 527.8, page verified True) [Brennan = yes 2026-10-18] - male end drill (column mapping: REPORT.md, table 5502); = OMi WebsitePartsInfo2026 Items!S1468 "Side 1 ID" = 0.406 (same value; OMi and Brennan count as one source); TAPDRILL@BORE: end library: tap drill of the -08 female NPTF port = 0.7 (gen_straight2 FPT[8] = templates/DesignTable_2405_SW2.xlsx TAPDRILL@BORE_A; = Air-Way's per-size tap drill of OPEN_QUESTIONS A1) [Q-TRANSFER-TAPDRILL = A1 answered YES 2026-10-18 (00_DOCS/ANSWERS_2026-10-18.md): Air-Way per-size tap drill on existing families]; THDMAJ_A1@DRIVE: end library: pipe OD of the -06 NPTF thread = 0.675 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[6], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_A2@DRIVE: end library: pipe OD of the -08 NPTF thread = 0.84 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[8], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; $PRP@Threads: thread callouts from the part number dashes in the format of the table's other rows; = Brennan TFA-p031-t03 thread columns (A1 NPTF 3/8-18, A2 NPTF 1/2-14) and OMi Items Side 1 / 2 / 3 Thread | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); female legs: the forged hex arm stops 0.26 short of the port face and the end is a ROUND COLLAR of dia = the hex flats - MEASURED on the Brennan 2502-06-04-FG, 5502-04-04/-08-08/-16-16-FG, 5504-08-08-FG and 5605-08-08-08-FG STEPs (collar 0.260 at every size and leg; single manufacturer); port-mouth 45deg chamfer and hex chamfers not modelled; female NPTF legs: Air-Way tap drill to MS51503 P1 max (Brennan 5405-08-08 STEP: 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED -08 only)), tapered helix over P1; connecting drill to the axis crossing = the part's own D column (ASSUMPTION; capped at the tap drill where larger); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 5502-06-08 dims are NOT assumed; confirm before modelling | 2026-10-18 Brennan = yes (wave2 tee_elbow, staged, not shipped): sizes from the Brennan TFA catalog (= OMi Items, one source), end details from the end library; marked $PRP@DimSource BRENNAN (to undo: clear the BRENNAN cells, set the row MISSING, regenerate)</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>5502-08-06-FG</t>
+          <t>5502-06-08-FG</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>5502-08-12-FG</t>
+          <t>5502-08-04-FG</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.59</v>
+        <v>1.47</v>
       </c>
       <c r="C11" t="n">
-        <v>0.655</v>
+        <v>0.4375</v>
       </c>
       <c r="D11" t="n">
         <v>0.40779</v>
@@ -2031,28 +2071,28 @@
         <v>0.2163</v>
       </c>
       <c r="H11" t="n">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="I11" t="n">
-        <v>0.655</v>
+        <v>0.4375</v>
       </c>
       <c r="J11" t="n">
         <v>0.53</v>
       </c>
       <c r="K11" t="n">
-        <v>1.59</v>
+        <v>1.47</v>
       </c>
       <c r="L11" t="n">
-        <v>0.91</v>
+        <v>0.43</v>
       </c>
       <c r="M11" t="n">
-        <v>0.91</v>
+        <v>0.67</v>
       </c>
       <c r="N11" t="n">
-        <v>0.53</v>
+        <v>0.43</v>
       </c>
       <c r="O11" t="n">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="P11" t="n">
         <v>0.81557</v>
@@ -2070,61 +2110,61 @@
         <v>0.35064</v>
       </c>
       <c r="U11" t="n">
-        <v>1.59</v>
+        <v>1.47</v>
       </c>
       <c r="V11" t="n">
-        <v>0.91</v>
+        <v>0.43</v>
       </c>
       <c r="W11" t="n">
-        <v>0.91</v>
+        <v>0.67</v>
       </c>
       <c r="X11" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.05556</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.455</v>
+        <v>0.215</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.51214</v>
+        <v>0.25944</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.31</v>
+        <v>0.875</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.84</v>
+        <v>0.72</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.31</v>
+        <v>0.875</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.1</v>
+        <v>0.75</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.655</v>
+        <v>0.4375</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.655</v>
+        <v>0.4375</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.37766</v>
+        <v>0.25209</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.37766</v>
+        <v>0.25209</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.75583</v>
+        <v>0.50468</v>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>5502-08-12-FG</t>
+          <t>5502-08-04-FG</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>90 deg Street Pipe Elbow, 1/2-14 NPTF x 3/4-14 NPTF (female)</t>
+          <t>90 deg Street Pipe Elbow, 1/2-14 NPTF x 1/4-18 NPTF (female)</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
@@ -2139,7 +2179,7 @@
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>3/4-14 NPTF (female)</t>
+          <t>1/4-18 NPTF (female)</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
@@ -2149,134 +2189,139 @@
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>Air-Way s128 only (double-pass 46 rows; page footer claimed 47); female NPTF per ANSI B1.20.3 | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); female legs: the forged hex arm stops 0.26 short of the port face and the end is a ROUND COLLAR of dia = the hex flats - MEASURED on the Brennan 2502-06-04-FG, 5502-04-04/-08-08/-16-16-FG, 5504-08-08-FG and 5605-08-08-08-FG STEPs (collar 0.260 at every size and leg; single manufacturer); port-mouth 45deg chamfer and hex chamfers not modelled; female NPTF legs: Air-Way tap drill to MS51503 P1 max (Brennan 5405-08-08 STEP: 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED -08 only)), tapered helix over P1; connecting drill to the axis crossing = the part's own D column (ASSUMPTION; capped at the tap drill where larger); each leg bore runs from its face to the axis crossing</t>
+          <t>Air-Way s128 only (double-pass 46 rows; page footer claimed 47); female NPTF per ANSI B1.20.3; W@REF: OMi WebsitePartsInfo2026.xlsx Items!R1469 Hex Flat = 0.875 (table had 1.06) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; N1@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P1469 = 1.010 (table had 1) [user 2026-10-18 A19] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); female legs: the forged hex arm stops 0.26 short of the port face and the end is a ROUND COLLAR of dia = the hex flats - MEASURED on the Brennan 2502-06-04-FG, 5502-04-04/-08-08/-16-16-FG, 5504-08-08-FG and 5605-08-08-08-FG STEPs (collar 0.260 at every size and leg; single manufacturer); port-mouth 45deg chamfer and hex chamfers not modelled; female NPTF legs: Air-Way tap drill to MS51503 P1 max (Brennan 5405-08-08 STEP: 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED -08 only)), tapered helix over P1; connecting drill to the axis crossing = the part's own D column (ASSUMPTION; capped at the tap drill where larger); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>A19 (user 2026-10-18, group 3 open): N1@DRIVE 1 -&gt; OMi 1.010 (Items!P1469, M110)</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>5502-08-12-FG</t>
+          <t>5502-08-04-FG</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>5502-20-20-FG</t>
+          <t>5502-08-06-FG</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.75</v>
+        <v>1.47</v>
       </c>
       <c r="C12" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.4375</v>
       </c>
       <c r="D12" t="n">
-        <v>0.81335</v>
+        <v>0.40779</v>
       </c>
       <c r="E12" t="n">
-        <v>0.7068</v>
+        <v>0.5337</v>
       </c>
       <c r="F12" t="n">
         <v>1.7899</v>
       </c>
       <c r="G12" t="n">
-        <v>0.2632</v>
+        <v>0.2163</v>
       </c>
       <c r="H12" t="n">
-        <v>1.7</v>
+        <v>1.02</v>
       </c>
       <c r="I12" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.4375</v>
       </c>
       <c r="J12" t="n">
-        <v>1.25</v>
+        <v>0.53</v>
       </c>
       <c r="K12" t="n">
-        <v>2.75</v>
+        <v>1.47</v>
       </c>
       <c r="L12" t="n">
-        <v>1.48</v>
+        <v>0.57</v>
       </c>
       <c r="M12" t="n">
-        <v>1.16</v>
+        <v>0.68</v>
       </c>
       <c r="N12" t="n">
-        <v>1.25</v>
+        <v>0.53</v>
       </c>
       <c r="O12" t="n">
-        <v>1.7</v>
+        <v>1.02</v>
       </c>
       <c r="P12" t="n">
-        <v>1.6267</v>
+        <v>0.81557</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.7068</v>
+        <v>0.5337</v>
       </c>
       <c r="R12" t="n">
-        <v>0.08696</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="S12" t="n">
-        <v>0.81335</v>
+        <v>0.40779</v>
       </c>
       <c r="T12" t="n">
-        <v>0.74378</v>
+        <v>0.35064</v>
       </c>
       <c r="U12" t="n">
-        <v>2.75</v>
+        <v>1.47</v>
       </c>
       <c r="V12" t="n">
-        <v>1.48</v>
+        <v>0.57</v>
       </c>
       <c r="W12" t="n">
-        <v>1.16</v>
+        <v>0.68</v>
       </c>
       <c r="X12" t="n">
-        <v>0.08696</v>
+        <v>0.05556</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.74</v>
+        <v>0.285</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.80957</v>
+        <v>0.32944</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.7</v>
+        <v>1.02</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.88</v>
+        <v>0.875</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.78</v>
+        <v>0.72</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.88</v>
+        <v>0.875</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.44</v>
+        <v>0.76</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.4375</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.4375</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.54221</v>
+        <v>0.25209</v>
       </c>
       <c r="AI12" t="n">
-        <v>0.54221</v>
+        <v>0.25209</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.08492</v>
+        <v>0.50468</v>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>5502-20-20-FG</t>
+          <t>5502-08-06-FG</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>90 deg Street Pipe Elbow, 1 1/4-11 1/2 NPTF x 1 1/4-11 1/2 NPTF (female)</t>
+          <t>90 deg Street Pipe Elbow, 1/2-14 NPTF x 3/8-18 NPTF (female)</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
@@ -2286,12 +2331,12 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>1 1/4-11 1/2 NPTF</t>
+          <t>1/2-14 NPTF</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>1 1/4-11 1/2 NPTF (female)</t>
+          <t>3/8-18 NPTF (female)</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
@@ -2301,139 +2346,139 @@
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>Air-Way s128 only (double-pass 46 rows; page footer claimed 47); female NPTF per ANSI B1.20.3 | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); female legs: the forged hex arm stops 0.26 short of the port face and the end is a ROUND COLLAR of dia = the hex flats - MEASURED on the Brennan 2502-06-04-FG, 5502-04-04/-08-08/-16-16-FG, 5504-08-08-FG and 5605-08-08-08-FG STEPs (collar 0.260 at every size and leg; single manufacturer); port-mouth 45deg chamfer and hex chamfers not modelled; female NPTF legs: Air-Way tap drill to MS51503 P1 max (Brennan 5405-08-08 STEP: 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED -08 only)), tapered helix over P1; connecting drill to the axis crossing = the part's own D column (ASSUMPTION; capped at the tap drill where larger); each leg bore runs from its face to the axis crossing</t>
+          <t>Air-Way s128 only (double-pass 46 rows; page footer claimed 47); female NPTF per ANSI B1.20.3; W@REF: OMi WebsitePartsInfo2026.xlsx Items!R1470 Hex Flat = 0.875 (table had 1.06) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; N1@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P1470 = 1.020 (table had 1.01) [user 2026-10-18 A19] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); female legs: the forged hex arm stops 0.26 short of the port face and the end is a ROUND COLLAR of dia = the hex flats - MEASURED on the Brennan 2502-06-04-FG, 5502-04-04/-08-08/-16-16-FG, 5504-08-08-FG and 5605-08-08-08-FG STEPs (collar 0.260 at every size and leg; single manufacturer); port-mouth 45deg chamfer and hex chamfers not modelled; female NPTF legs: Air-Way tap drill to MS51503 P1 max (Brennan 5405-08-08 STEP: 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED -08 only)), tapered helix over P1; connecting drill to the axis crossing = the part's own D column (ASSUMPTION; capped at the tap drill where larger); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>N 2.75 vs non-FG 2.38 (FG &gt; non-FG by .37, unusual) - as-printed</t>
+          <t>A19 (user 2026-10-18, group 3 open): N1@DRIVE 1.01 -&gt; OMi 1.020 (Items!P1470, M110)</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>5502-20-20-FG</t>
+          <t>5502-08-06-FG</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>5502-24-24-FG</t>
+          <t>5502-08-12-FG</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.05</v>
+        <v>1.59</v>
       </c>
       <c r="C13" t="n">
-        <v>1.28</v>
+        <v>0.655</v>
       </c>
       <c r="D13" t="n">
-        <v>0.93283</v>
+        <v>0.40779</v>
       </c>
       <c r="E13" t="n">
-        <v>0.7235</v>
+        <v>0.5337</v>
       </c>
       <c r="F13" t="n">
         <v>1.7899</v>
       </c>
       <c r="G13" t="n">
-        <v>0.2765</v>
+        <v>0.2163</v>
       </c>
       <c r="H13" t="n">
-        <v>2.08</v>
+        <v>1.36</v>
       </c>
       <c r="I13" t="n">
-        <v>1.28</v>
+        <v>0.655</v>
       </c>
       <c r="J13" t="n">
-        <v>1.5</v>
+        <v>0.53</v>
       </c>
       <c r="K13" t="n">
-        <v>3.05</v>
+        <v>1.59</v>
       </c>
       <c r="L13" t="n">
-        <v>1.72</v>
+        <v>0.91</v>
       </c>
       <c r="M13" t="n">
-        <v>1.16</v>
+        <v>0.91</v>
       </c>
       <c r="N13" t="n">
-        <v>1.5</v>
+        <v>0.53</v>
       </c>
       <c r="O13" t="n">
-        <v>2.08</v>
+        <v>1.36</v>
       </c>
       <c r="P13" t="n">
-        <v>1.86566</v>
+        <v>0.81557</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.7235</v>
+        <v>0.5337</v>
       </c>
       <c r="R13" t="n">
-        <v>0.08696</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="S13" t="n">
-        <v>0.93283</v>
+        <v>0.40779</v>
       </c>
       <c r="T13" t="n">
-        <v>0.86326</v>
+        <v>0.35064</v>
       </c>
       <c r="U13" t="n">
-        <v>3.05</v>
+        <v>1.59</v>
       </c>
       <c r="V13" t="n">
-        <v>1.72</v>
+        <v>0.91</v>
       </c>
       <c r="W13" t="n">
-        <v>1.16</v>
+        <v>0.91</v>
       </c>
       <c r="X13" t="n">
-        <v>0.08696</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.86</v>
+        <v>0.455</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.92957</v>
+        <v>0.51214</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.08</v>
+        <v>1.36</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.56</v>
+        <v>1.31</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.05</v>
+        <v>0.84</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.56</v>
+        <v>1.31</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.82</v>
+        <v>1.1</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.28</v>
+        <v>0.655</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.28</v>
+        <v>0.655</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.73851</v>
+        <v>0.37766</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.73851</v>
+        <v>0.37766</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.47752</v>
+        <v>0.75583</v>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>5502-24-24-FG</t>
+          <t>5502-08-12-FG</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>90 deg Street Pipe Elbow, 1 1/2-11 1/2 NPTF x 1 1/2-11 1/2 NPTF (female)</t>
+          <t>90 deg Street Pipe Elbow, 1/2-14 NPTF x 3/4-14 NPTF (female)</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
@@ -2443,17 +2488,17 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>1 1/2-11 1/2 NPTF</t>
+          <t>1/2-14 NPTF</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>1 1/2-11 1/2 NPTF (female)</t>
+          <t>3/4-14 NPTF (female)</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
@@ -2463,167 +2508,1266 @@
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>N 3.05 vs non-FG 2.70 - as-printed</t>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on W@REF=1.31~1.312; D@BORE=0.53~0.531</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>5502-24-24-FG</t>
+          <t>5502-08-12-FG</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>5502-32-32-FG</t>
+          <t>5502-12-08-FG</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>1.59</v>
       </c>
       <c r="C14" t="n">
-        <v>1.405</v>
+        <v>0.531</v>
       </c>
       <c r="D14" t="n">
-        <v>1.16929</v>
+        <v>0.51241</v>
       </c>
       <c r="E14" t="n">
-        <v>0.7565</v>
+        <v>0.5457</v>
       </c>
       <c r="F14" t="n">
         <v>1.7899</v>
       </c>
       <c r="G14" t="n">
+        <v>0.2043</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.531</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.719</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.02482</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.5457</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.07142999999999999</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.51241</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0.45527</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0.07142999999999999</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0.40714</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.062</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.062</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0.531</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0.531</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0.30607</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0.30607</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0.61265</v>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>5502-12-08-FG</t>
+        </is>
+      </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>90 deg Street Pipe Elbow, 3/4-14 NPTF x 1/2-14 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>5502</t>
+        </is>
+      </c>
+      <c r="AN14" t="inlineStr">
+        <is>
+          <t>3/4-14 NPTF</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>1/2-14 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="AP14" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 5502-12-08 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): N@DRIVE: Brennan TFA catalog p.31 table TFA-p031-t03 "5502-FG MP-FP 90 DEG ELBOW STREET ELBOW" row 5502-12-08-FG col "N LGTH" = "1.590" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 588.2, page verified True) [Brennan = yes 2026-10-18] - axis crossing to the male NPTF tip (column mapping: REPORT.md, table 5502); = OMi WebsitePartsInfo2026 Items!N1474 "M 1 Size" = 1.590 (same value; OMi and Brennan count as one source); N1@DRIVE: Brennan TFA catalog p.31 table TFA-p031-t03 "5502-FG MP-FP 90 DEG ELBOW STREET ELBOW" row 5502-12-08-FG col "N1 LGTH" = "1.230" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 588.2, page verified True) [Brennan = yes 2026-10-18] - axis crossing to the female NPTF port face (column mapping: REPORT.md, table 5502); = OMi WebsitePartsInfo2026 Items!P1474 "L 1 Size" = 1.230 (same value; OMi and Brennan count as one source); W@REF: Brennan TFA catalog p.31 table TFA-p031-t03 "5502-FG MP-FP 90 DEG ELBOW STREET ELBOW" row 5502-12-08-FG col "Y FLATS" = "1.062" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 588.2, page verified True) [Brennan = yes 2026-10-18] - forged body flats (column mapping: REPORT.md, table 5502); = OMi WebsitePartsInfo2026 Items!R1474 "Hex Flat" = 1.062 (same value; OMi and Brennan count as one source); D@BORE: Brennan TFA catalog p.31 table TFA-p031-t03 "5502-FG MP-FP 90 DEG ELBOW STREET ELBOW" row 5502-12-08-FG col "A1 DRILL" = "0.719" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 588.2, page verified True) [Brennan = yes 2026-10-18] - male end drill (column mapping: REPORT.md, table 5502); = OMi WebsitePartsInfo2026 Items!S1474 "Side 1 ID" = 0.719 (same value; OMi and Brennan count as one source); TAPDRILL@BORE: end library: tap drill of the -08 female NPTF port = 0.7 (gen_straight2 FPT[8] = templates/DesignTable_2405_SW2.xlsx TAPDRILL@BORE_A; = Air-Way's per-size tap drill of OPEN_QUESTIONS A1) [Q-TRANSFER-TAPDRILL = A1 answered YES 2026-10-18 (00_DOCS/ANSWERS_2026-10-18.md): Air-Way per-size tap drill on existing families]; THDMAJ_A1@DRIVE: end library: pipe OD of the -12 NPTF thread = 1.05 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[12], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_A2@DRIVE: end library: pipe OD of the -08 NPTF thread = 0.84 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[8], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; $PRP@Threads: thread callouts from the part number dashes in the format of the table's other rows; = Brennan TFA-p031-t03 thread columns (A1 NPTF 3/4-14, A2 NPTF 1/2-14) and OMi Items Side 1 / 2 / 3 Thread | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); female legs: the forged hex arm stops 0.26 short of the port face and the end is a ROUND COLLAR of dia = the hex flats - MEASURED on the Brennan 2502-06-04-FG, 5502-04-04/-08-08/-16-16-FG, 5504-08-08-FG and 5605-08-08-08-FG STEPs (collar 0.260 at every size and leg; single manufacturer); port-mouth 45deg chamfer and hex chamfers not modelled; female NPTF legs: Air-Way tap drill to MS51503 P1 max (Brennan 5405-08-08 STEP: 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED -08 only)), tapered helix over P1; connecting drill to the axis crossing = the part's own D column (ASSUMPTION; capped at the tap drill where larger); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 5502-12-08 dims are NOT assumed; confirm before modelling | 2026-10-18 Brennan = yes (wave2 tee_elbow, staged, not shipped): sizes from the Brennan TFA catalog (= OMi Items, one source), end details from the end library; marked $PRP@DimSource BRENNAN (to undo: clear the BRENNAN cells, set the row MISSING, regenerate) | leg 1: male NPTF thread dia at L2 1.0589 vs hex flats 1.0620 (round end flush with the flats by 0.0015; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012)</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>5502-12-08-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>5502-12-12-FG</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.655</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.51241</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.5457</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.2043</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.655</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.02482</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.5457</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.07142999999999999</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.51241</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0.45527</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0.07142999999999999</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0.51214</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0.655</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0.655</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0.37766</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>0.37766</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0.75583</v>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>5502-12-12-FG</t>
+        </is>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>90 deg Street Pipe Elbow, 3/4-14 NPTF x 3/4-14 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>5502</t>
+        </is>
+      </c>
+      <c r="AN15" t="inlineStr">
+        <is>
+          <t>3/4-14 NPTF</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>3/4-14 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="AP15" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="AQ15" t="inlineStr">
+        <is>
+          <t>Air-Way s128 only (double-pass 46 rows; page footer claimed 47); female NPTF per ANSI B1.20.3 | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); female legs: the forged hex arm stops 0.26 short of the port face and the end is a ROUND COLLAR of dia = the hex flats - MEASURED on the Brennan 2502-06-04-FG, 5502-04-04/-08-08/-16-16-FG, 5504-08-08-FG and 5605-08-08-08-FG STEPs (collar 0.260 at every size and leg; single manufacturer); port-mouth 45deg chamfer and hex chamfers not modelled; female NPTF legs: Air-Way tap drill to MS51503 P1 max (Brennan 5405-08-08 STEP: 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED -08 only)), tapered helix over P1; connecting drill to the axis crossing = the part's own D column (ASSUMPTION; capped at the tap drill where larger); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>DROP: no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-16: BUILD - the DROP above is void: OMi sells this part, the 2026-09-23 crawl had dropped its SKU | Brennan TFA TFA-p031-t03: agrees on N@DRIVE, N1@DRIVE, W@REF, D@BORE</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>5502-12-12-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>5502-16-12-FG</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.656</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.6415999999999999</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.6828</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.2572</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.656</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.2832</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.6828</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.08696</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.6415999999999999</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0.57203</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0.07142999999999999</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0.51214</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0.656</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0.656</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0.37824</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>0.37824</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0.75698</v>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>5502-16-12-FG</t>
+        </is>
+      </c>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>90 deg Street Pipe Elbow, 1-11 1/2 NPTF x 3/4-14 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>5502</t>
+        </is>
+      </c>
+      <c r="AN16" t="inlineStr">
+        <is>
+          <t>1-11 1/2 NPTF</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>3/4-14 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="AP16" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AQ16" t="inlineStr">
+        <is>
+          <t>Air-Way s128 only (double-pass 46 rows; page footer claimed 47); female NPTF per ANSI B1.20.3 | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); female legs: the forged hex arm stops 0.26 short of the port face and the end is a ROUND COLLAR of dia = the hex flats - MEASURED on the Brennan 2502-06-04-FG, 5502-04-04/-08-08/-16-16-FG, 5504-08-08-FG and 5605-08-08-08-FG STEPs (collar 0.260 at every size and leg; single manufacturer); port-mouth 45deg chamfer and hex chamfers not modelled; female NPTF legs: Air-Way tap drill to MS51503 P1 max (Brennan 5405-08-08 STEP: 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED -08 only)), tapered helix over P1; connecting drill to the axis crossing = the part's own D column (ASSUMPTION; capped at the tap drill where larger); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>DROP: no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-16: BUILD - the DROP above is void: OMi sells this part, the 2026-09-23 crawl had dropped its SKU | OMi dims first (user 2026-09-25): W@REF: OMi WebsitePartsInfo2026.xlsx Items!R1477 = 1.312 (table had 1.63) | Brennan TFA TFA-p031-t03: agrees on N@DRIVE, W@REF, D@BORE; DIFFERS on N1@DRIVE 1.39 vs Brennan N1 LGTH 1.360 (built to the dimension source, s6) | A19-style (user 2026-10-18 'yes, apply the 7 pending OMi values'): N1@DRIVE 1.39 -&gt; 1.36 | leg 1: male NPTF thread dia at L2 1.3259 vs hex flats 1.3120 (round end proud of the flats by 0.0069; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012)</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>5502-16-12-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>5502-16-16-FG</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.6415999999999999</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.6828</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.2572</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.2832</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.6828</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.08696</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.6415999999999999</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0.57203</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0.08696</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0.63957</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>0.47004</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>0.47004</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0.94058</v>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>5502-16-16-FG</t>
+        </is>
+      </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>90 deg Street Pipe Elbow, 1-11 1/2 NPTF x 1-11 1/2 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>5502</t>
+        </is>
+      </c>
+      <c r="AN17" t="inlineStr">
+        <is>
+          <t>1-11 1/2 NPTF</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>1-11 1/2 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="AP17" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="AQ17" t="inlineStr">
+        <is>
+          <t>Air-Way s128 only (double-pass 46 rows; page footer claimed 47); female NPTF per ANSI B1.20.3 | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); female legs: the forged hex arm stops 0.26 short of the port face and the end is a ROUND COLLAR of dia = the hex flats - MEASURED on the Brennan 2502-06-04-FG, 5502-04-04/-08-08/-16-16-FG, 5504-08-08-FG and 5605-08-08-08-FG STEPs (collar 0.260 at every size and leg; single manufacturer); port-mouth 45deg chamfer and hex chamfers not modelled; female NPTF legs: Air-Way tap drill to MS51503 P1 max (Brennan 5405-08-08 STEP: 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED -08 only)), tapered helix over P1; connecting drill to the axis crossing = the part's own D column (ASSUMPTION; capped at the tap drill where larger); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>DROP: no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-16: BUILD - the DROP above is void: OMi sells this part, the 2026-09-23 crawl had dropped its SKU | Brennan TFA TFA-p031-t03: agrees on N@DRIVE, N1@DRIVE, W@REF, D@BORE</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr">
+        <is>
+          <t>5502-16-16-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>5502-20-16-FG</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.81335</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.7068</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.2632</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="N18" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.6267</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.7068</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.08696</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.81335</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0.74378</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0.08696</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0.63957</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>0.4686</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>0.4686</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>0.93769</v>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>5502-20-16-FG</t>
+        </is>
+      </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t>90 deg Street Pipe Elbow, 1 1/4-11 1/2 NPTF x 1-11 1/2 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>5502</t>
+        </is>
+      </c>
+      <c r="AN18" t="inlineStr">
+        <is>
+          <t>1 1/4-11 1/2 NPTF</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>1-11 1/2 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="AP18" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AQ18" t="inlineStr">
+        <is>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 5502-20-16 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): N@DRIVE: Brennan TFA catalog p.31 table TFA-p031-t03 "5502-FG MP-FP 90 DEG ELBOW STREET ELBOW" row 5502-20-16-FG col "N LGTH" = "2.380" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 648.7, page verified True) [Brennan = yes 2026-10-18] - axis crossing to the male NPTF tip (column mapping: REPORT.md, table 5502); = OMi WebsitePartsInfo2026 Items!N1480 "M 1 Size" = 2.380 (same value; OMi and Brennan count as one source); N1@DRIVE: Brennan TFA catalog p.31 table TFA-p031-t03 "5502-FG MP-FP 90 DEG ELBOW STREET ELBOW" row 5502-20-16-FG col "N1 LGTH" = "1.620" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 648.7, page verified True) [Brennan = yes 2026-10-18] - axis crossing to the female NPTF port face (column mapping: REPORT.md, table 5502); = OMi WebsitePartsInfo2026 Items!P1480 "L 1 Size" = 1.620 (same value; OMi and Brennan count as one source); W@REF: Brennan TFA catalog p.31 table TFA-p031-t03 "5502-FG MP-FP 90 DEG ELBOW STREET ELBOW" row 5502-20-16-FG col "Y FLATS" = "1.625" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 648.7, page verified True) [Brennan = yes 2026-10-18] - forged body flats (column mapping: REPORT.md, table 5502); = OMi WebsitePartsInfo2026 Items!R1480 "Hex Flat" = 1.625 (same value; OMi and Brennan count as one source); D@BORE: Brennan TFA catalog p.31 table TFA-p031-t03 "5502-FG MP-FP 90 DEG ELBOW STREET ELBOW" row 5502-20-16-FG col "A1 DRILL" = "1.250" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 648.7, page verified True) [Brennan = yes 2026-10-18] - male end drill (column mapping: REPORT.md, table 5502); = OMi WebsitePartsInfo2026 Items!S1480 "Side 1 ID" = 1.250 (same value; OMi and Brennan count as one source); TAPDRILL@BORE: end library: tap drill of the -16 female NPTF port = 1.14 (gen_straight2 FPT[16] = templates/DesignTable_2405_SW2.xlsx TAPDRILL@BORE_A; = Air-Way's per-size tap drill of OPEN_QUESTIONS A1) [Q-TRANSFER-TAPDRILL = A1 answered YES 2026-10-18 (00_DOCS/ANSWERS_2026-10-18.md): Air-Way per-size tap drill on existing families]; THDMAJ_A1@DRIVE: end library: pipe OD of the -20 NPTF thread = 1.66 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[20], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_A2@DRIVE: end library: pipe OD of the -16 NPTF thread = 1.315 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[16], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; $PRP@Threads: thread callouts from the part number dashes in the format of the table's other rows; = Brennan TFA-p031-t03 thread columns (A1 NPTF 1-1/4-11-1/2, A2 NPTF 1-11-1/2) and OMi Items Side 1 / 2 / 3 Thread | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); female legs: the forged hex arm stops 0.26 short of the port face and the end is a ROUND COLLAR of dia = the hex flats - MEASURED on the Brennan 2502-06-04-FG, 5502-04-04/-08-08/-16-16-FG, 5504-08-08-FG and 5605-08-08-08-FG STEPs (collar 0.260 at every size and leg; single manufacturer); port-mouth 45deg chamfer and hex chamfers not modelled; female NPTF legs: Air-Way tap drill to MS51503 P1 max (Brennan 5405-08-08 STEP: 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED -08 only)), tapered helix over P1; connecting drill to the axis crossing = the part's own D column (ASSUMPTION; capped at the tap drill where larger); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 5502-20-16 dims are NOT assumed; confirm before modelling | 2026-10-18 Brennan = yes (wave2 tee_elbow, staged, not shipped): sizes from the Brennan TFA catalog (= OMi Items, one source), end details from the end library; marked $PRP@DimSource BRENNAN (to undo: clear the BRENNAN cells, set the row MISSING, regenerate) | leg 1: male NPTF thread dia at L2 1.6709 vs hex flats 1.6250 (round end proud of the flats by 0.0229; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012)</t>
+        </is>
+      </c>
+      <c r="AS18" t="inlineStr">
+        <is>
+          <t>5502-20-16-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>5502-20-20-FG</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.81335</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.7068</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.2632</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.6267</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.7068</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.08696</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.81335</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0.74378</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0.08696</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0.80957</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>0.54221</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>0.54221</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1.08492</v>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>5502-20-20-FG</t>
+        </is>
+      </c>
+      <c r="AL19" t="inlineStr">
+        <is>
+          <t>90 deg Street Pipe Elbow, 1 1/4-11 1/2 NPTF x 1 1/4-11 1/2 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>5502</t>
+        </is>
+      </c>
+      <c r="AN19" t="inlineStr">
+        <is>
+          <t>1 1/4-11 1/2 NPTF</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>1 1/4-11 1/2 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="AP19" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AQ19" t="inlineStr">
+        <is>
+          <t>Air-Way s128 only (double-pass 46 rows; page footer claimed 47); female NPTF per ANSI B1.20.3; N@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!N1481 = 2.380 (table had 2.75) [user 2026-10-18 A19] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); female legs: the forged hex arm stops 0.26 short of the port face and the end is a ROUND COLLAR of dia = the hex flats - MEASURED on the Brennan 2502-06-04-FG, 5502-04-04/-08-08/-16-16-FG, 5504-08-08-FG and 5605-08-08-08-FG STEPs (collar 0.260 at every size and leg; single manufacturer); port-mouth 45deg chamfer and hex chamfers not modelled; female NPTF legs: Air-Way tap drill to MS51503 P1 max (Brennan 5405-08-08 STEP: 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED -08 only)), tapered helix over P1; connecting drill to the axis crossing = the part's own D column (ASSUMPTION; capped at the tap drill where larger); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>N 2.75 vs non-FG 2.38 (FG &gt; non-FG by .37, unusual) - as-printed | A19 (user 2026-10-18, group 3 open): N@DRIVE 2.75 -&gt; OMi 2.380 (Items!N1481, M109)</t>
+        </is>
+      </c>
+      <c r="AS19" t="inlineStr">
+        <is>
+          <t>5502-20-20-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>5502-24-24-FG</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.93283</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.7235</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.2765</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O20" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.86566</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.7235</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.08696</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0.93283</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0.86326</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0.08696</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0.92957</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>0.73851</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>0.73851</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1.47752</v>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>5502-24-24-FG</t>
+        </is>
+      </c>
+      <c r="AL20" t="inlineStr">
+        <is>
+          <t>90 deg Street Pipe Elbow, 1 1/2-11 1/2 NPTF x 1 1/2-11 1/2 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>5502</t>
+        </is>
+      </c>
+      <c r="AN20" t="inlineStr">
+        <is>
+          <t>1 1/2-11 1/2 NPTF</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>1 1/2-11 1/2 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="AP20" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AQ20" t="inlineStr">
+        <is>
+          <t>Air-Way s128 only (double-pass 46 rows; page footer claimed 47); female NPTF per ANSI B1.20.3; N@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!N1484 = 2.640 (table had 3.05) [user 2026-10-18 A19] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); female legs: the forged hex arm stops 0.26 short of the port face and the end is a ROUND COLLAR of dia = the hex flats - MEASURED on the Brennan 2502-06-04-FG, 5502-04-04/-08-08/-16-16-FG, 5504-08-08-FG and 5605-08-08-08-FG STEPs (collar 0.260 at every size and leg; single manufacturer); port-mouth 45deg chamfer and hex chamfers not modelled; female NPTF legs: Air-Way tap drill to MS51503 P1 max (Brennan 5405-08-08 STEP: 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED -08 only)), tapered helix over P1; connecting drill to the axis crossing = the part's own D column (ASSUMPTION; capped at the tap drill where larger); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>N 3.05 vs non-FG 2.70 - as-printed | A19 (user 2026-10-18, group 3 open): N@DRIVE 3.05 -&gt; OMi 2.640 (Items!N1484, M109)</t>
+        </is>
+      </c>
+      <c r="AS20" t="inlineStr">
+        <is>
+          <t>5502-24-24-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>5502-32-32-FG</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>3</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1.405</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1.16929</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.7565</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="G21" t="n">
         <v>0.2735</v>
       </c>
-      <c r="H14" t="n">
+      <c r="H21" t="n">
         <v>2.39</v>
       </c>
-      <c r="I14" t="n">
+      <c r="I21" t="n">
         <v>1.405</v>
       </c>
-      <c r="J14" t="n">
+      <c r="J21" t="n">
         <v>1.94</v>
       </c>
-      <c r="K14" t="n">
+      <c r="K21" t="n">
         <v>3</v>
       </c>
-      <c r="L14" t="n">
+      <c r="L21" t="n">
         <v>2.2</v>
       </c>
-      <c r="M14" t="n">
+      <c r="M21" t="n">
         <v>1.18</v>
       </c>
-      <c r="N14" t="n">
+      <c r="N21" t="n">
         <v>1.94</v>
       </c>
-      <c r="O14" t="n">
+      <c r="O21" t="n">
         <v>2.39</v>
       </c>
-      <c r="P14" t="n">
+      <c r="P21" t="n">
         <v>2.33859</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="Q21" t="n">
         <v>0.7565</v>
       </c>
-      <c r="R14" t="n">
+      <c r="R21" t="n">
         <v>0.08696</v>
       </c>
-      <c r="S14" t="n">
+      <c r="S21" t="n">
         <v>1.16929</v>
       </c>
-      <c r="T14" t="n">
+      <c r="T21" t="n">
         <v>1.09973</v>
       </c>
-      <c r="U14" t="n">
+      <c r="U21" t="n">
         <v>3</v>
       </c>
-      <c r="V14" t="n">
+      <c r="V21" t="n">
         <v>2.2</v>
       </c>
-      <c r="W14" t="n">
+      <c r="W21" t="n">
         <v>1.18</v>
       </c>
-      <c r="X14" t="n">
+      <c r="X21" t="n">
         <v>0.08696</v>
       </c>
-      <c r="Y14" t="n">
+      <c r="Y21" t="n">
         <v>1.1</v>
       </c>
-      <c r="Z14" t="n">
+      <c r="Z21" t="n">
         <v>1.16957</v>
       </c>
-      <c r="AA14" t="n">
+      <c r="AA21" t="n">
         <v>2.39</v>
       </c>
-      <c r="AB14" t="n">
+      <c r="AB21" t="n">
         <v>2.81</v>
       </c>
-      <c r="AC14" t="n">
+      <c r="AC21" t="n">
         <v>1.97</v>
       </c>
-      <c r="AD14" t="n">
+      <c r="AD21" t="n">
         <v>2.81</v>
       </c>
-      <c r="AE14" t="n">
+      <c r="AE21" t="n">
         <v>2.13</v>
       </c>
-      <c r="AF14" t="n">
+      <c r="AF21" t="n">
         <v>1.405</v>
       </c>
-      <c r="AG14" t="n">
+      <c r="AG21" t="n">
         <v>1.405</v>
       </c>
-      <c r="AH14" t="n">
+      <c r="AH21" t="n">
         <v>0.81068</v>
       </c>
-      <c r="AI14" t="n">
+      <c r="AI21" t="n">
         <v>0.81068</v>
       </c>
-      <c r="AJ14" t="n">
+      <c r="AJ21" t="n">
         <v>1.62185</v>
       </c>
-      <c r="AK14" t="inlineStr">
+      <c r="AK21" t="inlineStr">
         <is>
           <t>5502-32-32-FG</t>
         </is>
       </c>
-      <c r="AL14" t="inlineStr">
+      <c r="AL21" t="inlineStr">
         <is>
           <t>90 deg Street Pipe Elbow, 2-11 1/2 NPTF x 2-11 1/2 NPTF (female)</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
+      <c r="AM21" t="inlineStr">
         <is>
           <t>5502</t>
         </is>
       </c>
-      <c r="AN14" t="inlineStr">
+      <c r="AN21" t="inlineStr">
         <is>
           <t>2-11 1/2 NPTF</t>
         </is>
       </c>
-      <c r="AO14" t="inlineStr">
+      <c r="AO21" t="inlineStr">
         <is>
           <t>2-11 1/2 NPTF (female)</t>
         </is>
       </c>
-      <c r="AP14" t="inlineStr">
-        <is>
-          <t>ASSUMED</t>
-        </is>
-      </c>
-      <c r="AQ14" t="inlineStr">
+      <c r="AP21" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="AQ21" t="inlineStr">
         <is>
           <t>Air-Way s128 only (double-pass 46 rows; page footer claimed 47); female NPTF per ANSI B1.20.3 | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); female legs: the forged hex arm stops 0.26 short of the port face and the end is a ROUND COLLAR of dia = the hex flats - MEASURED on the Brennan 2502-06-04-FG, 5502-04-04/-08-08/-16-16-FG, 5504-08-08-FG and 5605-08-08-08-FG STEPs (collar 0.260 at every size and leg; single manufacturer); port-mouth 45deg chamfer and hex chamfers not modelled; female NPTF legs: Air-Way tap drill to MS51503 P1 max (Brennan 5405-08-08 STEP: 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED -08 only)), tapered helix over P1; connecting drill to the axis crossing = the part's own D column (ASSUMPTION; capped at the tap drill where larger); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>tap drill 2.20 vs non-FG 2.19 same thread - as-printed</t>
-        </is>
-      </c>
-      <c r="AS14" t="inlineStr">
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>tap drill 2.20 vs non-FG 2.19 same thread - as-printed | A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on W@REF=2.81~2.812; D@BORE=1.94~1.938</t>
+        </is>
+      </c>
+      <c r="AS21" t="inlineStr">
         <is>
           <t>5502-32-32-FG</t>
         </is>

--- a/04_DESIGN_TABLES/DesignTable_5502_SW2.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_5502_SW2.xlsx
@@ -802,7 +802,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.78</v>
+        <v>0.89</v>
       </c>
       <c r="C3" t="n">
         <v>0.28</v>
@@ -829,7 +829,7 @@
         <v>0.19</v>
       </c>
       <c r="K3" t="n">
-        <v>0.78</v>
+        <v>0.89</v>
       </c>
       <c r="L3" t="n">
         <v>0.33</v>
@@ -859,7 +859,7 @@
         <v>0.16694</v>
       </c>
       <c r="U3" t="n">
-        <v>0.78</v>
+        <v>0.89</v>
       </c>
       <c r="V3" t="n">
         <v>0.33</v>
@@ -883,7 +883,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.4</v>
+        <v>0.51</v>
       </c>
       <c r="AD3" t="n">
         <v>0.5600000000000001</v>
@@ -938,12 +938,12 @@
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>Air-Way s128 only (double-pass 46 rows; page footer claimed 47); female NPTF per ANSI B1.20.3; N@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!N1458 = 0.780 (table had 0.89) [user 2026-10-18 A19] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); female legs: the forged hex arm stops 0.26 short of the port face and the end is a ROUND COLLAR of dia = the hex flats - MEASURED on the Brennan 2502-06-04-FG, 5502-04-04/-08-08/-16-16-FG, 5504-08-08-FG and 5605-08-08-08-FG STEPs (collar 0.260 at every size and leg; single manufacturer); port-mouth 45deg chamfer and hex chamfers not modelled; female NPTF legs: Air-Way tap drill to MS51503 P1 max (Brennan 5405-08-08 STEP: 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED -08 only)), tapered helix over P1; connecting drill to the axis crossing = the part's own D column (ASSUMPTION; capped at the tap drill where larger); each leg bore runs from its face to the axis crossing</t>
+          <t>Air-Way s128 only (double-pass 46 rows; page footer claimed 47); female NPTF per ANSI B1.20.3; N@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!N1458 = 0.780 (table had 0.89) [user 2026-10-18 A19]; N@DRIVE: Air-Way 0.89 (raw 07_RAW_EXTRACTS; OMi file / Brennan 0.78) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); female legs: the forged hex arm stops 0.26 short of the port face and the end is a ROUND COLLAR of dia = the hex flats - MEASURED on the Brennan 2502-06-04-FG, 5502-04-04/-08-08/-16-16-FG, 5504-08-08-FG and 5605-08-08-08-FG STEPs (collar 0.260 at every size and leg; single manufacturer); port-mouth 45deg chamfer and hex chamfers not modelled; female NPTF legs: Air-Way tap drill to MS51503 P1 max (Brennan 5405-08-08 STEP: 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED -08 only)), tapered helix over P1; connecting drill to the axis crossing = the part's own D column (ASSUMPTION; capped at the tap drill where larger); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>A19 (user 2026-10-18, group 3 open): N@DRIVE 0.89 -&gt; OMi 0.780 (Items!N1458, M109)</t>
+          <t>A19 (user 2026-10-18, group 3 open): N@DRIVE 0.89 -&gt; OMi 0.780 (Items!N1458, M109) | 2026-10-20 Air-Way first: N@DRIVE OMi/Brennan 0.78 -&gt; Air-Way 0.89</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1119,7 +1119,7 @@
         <v>1.09</v>
       </c>
       <c r="C5" t="n">
-        <v>0.281</v>
+        <v>0.375</v>
       </c>
       <c r="D5" t="n">
         <v>0.26092</v>
@@ -1137,7 +1137,7 @@
         <v>0.67</v>
       </c>
       <c r="I5" t="n">
-        <v>0.281</v>
+        <v>0.375</v>
       </c>
       <c r="J5" t="n">
         <v>0.28</v>
@@ -1194,31 +1194,31 @@
         <v>0.67</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.75</v>
       </c>
       <c r="AC5" t="n">
         <v>0.53</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.75</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.41</v>
+        <v>0.463</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.281</v>
+        <v>0.375</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.281</v>
+        <v>0.375</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.16174</v>
+        <v>0.21601</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.16174</v>
+        <v>0.21601</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.32397</v>
+        <v>0.43251</v>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
@@ -1252,7 +1252,12 @@
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>Air-Way s128 only (double-pass 46 rows; page footer claimed 47); female NPTF per ANSI B1.20.3; W@REF: OMi WebsitePartsInfo2026.xlsx Items!R1461 Hex Flat = 0.562 (table had 0.75) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); female legs: the forged hex arm stops 0.26 short of the port face and the end is a ROUND COLLAR of dia = the hex flats - MEASURED on the Brennan 2502-06-04-FG, 5502-04-04/-08-08/-16-16-FG, 5504-08-08-FG and 5605-08-08-08-FG STEPs (collar 0.260 at every size and leg; single manufacturer); port-mouth 45deg chamfer and hex chamfers not modelled; female NPTF legs: Air-Way tap drill to MS51503 P1 max (Brennan 5405-08-08 STEP: 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED -08 only)), tapered helix over P1; connecting drill to the axis crossing = the part's own D column (ASSUMPTION; capped at the tap drill where larger); each leg bore runs from its face to the axis crossing</t>
+          <t>Air-Way s128 only (double-pass 46 rows; page footer claimed 47); female NPTF per ANSI B1.20.3; W@REF: OMi WebsitePartsInfo2026.xlsx Items!R1461 Hex Flat = 0.562 (table had 0.75) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; W@REF: Air-Way 0.75 (raw 07_RAW_EXTRACTS; OMi file / Brennan 0.562) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); female legs: the forged hex arm stops 0.26 short of the port face and the end is a ROUND COLLAR of dia = the hex flats - MEASURED on the Brennan 2502-06-04-FG, 5502-04-04/-08-08/-16-16-FG, 5504-08-08-FG and 5605-08-08-08-FG STEPs (collar 0.260 at every size and leg; single manufacturer); port-mouth 45deg chamfer and hex chamfers not modelled; female NPTF legs: Air-Way tap drill to MS51503 P1 max (Brennan 5405-08-08 STEP: 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED -08 only)), tapered helix over P1; connecting drill to the axis crossing = the part's own D column (ASSUMPTION; capped at the tap drill where larger); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: W@REF OMi/Brennan 0.562 -&gt; Air-Way 0.75 | leg 2 hex arm 0.463 barely clears the corner puck (radius 0.433)</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2056,7 +2061,7 @@
         <v>1.47</v>
       </c>
       <c r="C11" t="n">
-        <v>0.4375</v>
+        <v>0.53</v>
       </c>
       <c r="D11" t="n">
         <v>0.40779</v>
@@ -2071,10 +2076,10 @@
         <v>0.2163</v>
       </c>
       <c r="H11" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>0.4375</v>
+        <v>0.53</v>
       </c>
       <c r="J11" t="n">
         <v>0.53</v>
@@ -2092,7 +2097,7 @@
         <v>0.43</v>
       </c>
       <c r="O11" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="P11" t="n">
         <v>0.81557</v>
@@ -2128,34 +2133,34 @@
         <v>0.25944</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.875</v>
+        <v>1.06</v>
       </c>
       <c r="AC11" t="n">
         <v>0.72</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.875</v>
+        <v>1.06</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.75</v>
+        <v>0.74</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.4375</v>
+        <v>0.53</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.4375</v>
+        <v>0.53</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.25209</v>
+        <v>0.3055</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.25209</v>
+        <v>0.3055</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.50468</v>
+        <v>0.61149</v>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
@@ -2189,12 +2194,12 @@
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>Air-Way s128 only (double-pass 46 rows; page footer claimed 47); female NPTF per ANSI B1.20.3; W@REF: OMi WebsitePartsInfo2026.xlsx Items!R1469 Hex Flat = 0.875 (table had 1.06) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; N1@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P1469 = 1.010 (table had 1) [user 2026-10-18 A19] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); female legs: the forged hex arm stops 0.26 short of the port face and the end is a ROUND COLLAR of dia = the hex flats - MEASURED on the Brennan 2502-06-04-FG, 5502-04-04/-08-08/-16-16-FG, 5504-08-08-FG and 5605-08-08-08-FG STEPs (collar 0.260 at every size and leg; single manufacturer); port-mouth 45deg chamfer and hex chamfers not modelled; female NPTF legs: Air-Way tap drill to MS51503 P1 max (Brennan 5405-08-08 STEP: 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED -08 only)), tapered helix over P1; connecting drill to the axis crossing = the part's own D column (ASSUMPTION; capped at the tap drill where larger); each leg bore runs from its face to the axis crossing</t>
+          <t>Air-Way s128 only (double-pass 46 rows; page footer claimed 47); female NPTF per ANSI B1.20.3; W@REF: OMi WebsitePartsInfo2026.xlsx Items!R1469 Hex Flat = 0.875 (table had 1.06) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; N1@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P1469 = 1.010 (table had 1) [user 2026-10-18 A19]; N1@DRIVE: Air-Way 1 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.01) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; W@REF: Air-Way 1.06 (raw 07_RAW_EXTRACTS; OMi file / Brennan 0.875) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); female legs: the forged hex arm stops 0.26 short of the port face and the end is a ROUND COLLAR of dia = the hex flats - MEASURED on the Brennan 2502-06-04-FG, 5502-04-04/-08-08/-16-16-FG, 5504-08-08-FG and 5605-08-08-08-FG STEPs (collar 0.260 at every size and leg; single manufacturer); port-mouth 45deg chamfer and hex chamfers not modelled; female NPTF legs: Air-Way tap drill to MS51503 P1 max (Brennan 5405-08-08 STEP: 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED -08 only)), tapered helix over P1; connecting drill to the axis crossing = the part's own D column (ASSUMPTION; capped at the tap drill where larger); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>A19 (user 2026-10-18, group 3 open): N1@DRIVE 1 -&gt; OMi 1.010 (Items!P1469, M110)</t>
+          <t>A19 (user 2026-10-18, group 3 open): N1@DRIVE 1 -&gt; OMi 1.010 (Items!P1469, M110) | 2026-10-20 Air-Way first: N1@DRIVE OMi/Brennan 1.01 -&gt; Air-Way 1 | 2026-10-20 Air-Way first: W@REF OMi/Brennan 0.875 -&gt; Air-Way 1.06</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -2213,7 +2218,7 @@
         <v>1.47</v>
       </c>
       <c r="C12" t="n">
-        <v>0.4375</v>
+        <v>0.53</v>
       </c>
       <c r="D12" t="n">
         <v>0.40779</v>
@@ -2228,10 +2233,10 @@
         <v>0.2163</v>
       </c>
       <c r="H12" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4375</v>
+        <v>0.53</v>
       </c>
       <c r="J12" t="n">
         <v>0.53</v>
@@ -2249,7 +2254,7 @@
         <v>0.53</v>
       </c>
       <c r="O12" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="P12" t="n">
         <v>0.81557</v>
@@ -2285,34 +2290,34 @@
         <v>0.32944</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.875</v>
+        <v>1.06</v>
       </c>
       <c r="AC12" t="n">
         <v>0.72</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.875</v>
+        <v>1.06</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.76</v>
+        <v>0.75</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.4375</v>
+        <v>0.53</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.4375</v>
+        <v>0.53</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.25209</v>
+        <v>0.3055</v>
       </c>
       <c r="AI12" t="n">
-        <v>0.25209</v>
+        <v>0.3055</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.50468</v>
+        <v>0.61149</v>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
@@ -2346,12 +2351,12 @@
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>Air-Way s128 only (double-pass 46 rows; page footer claimed 47); female NPTF per ANSI B1.20.3; W@REF: OMi WebsitePartsInfo2026.xlsx Items!R1470 Hex Flat = 0.875 (table had 1.06) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; N1@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P1470 = 1.020 (table had 1.01) [user 2026-10-18 A19] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); female legs: the forged hex arm stops 0.26 short of the port face and the end is a ROUND COLLAR of dia = the hex flats - MEASURED on the Brennan 2502-06-04-FG, 5502-04-04/-08-08/-16-16-FG, 5504-08-08-FG and 5605-08-08-08-FG STEPs (collar 0.260 at every size and leg; single manufacturer); port-mouth 45deg chamfer and hex chamfers not modelled; female NPTF legs: Air-Way tap drill to MS51503 P1 max (Brennan 5405-08-08 STEP: 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED -08 only)), tapered helix over P1; connecting drill to the axis crossing = the part's own D column (ASSUMPTION; capped at the tap drill where larger); each leg bore runs from its face to the axis crossing</t>
+          <t>Air-Way s128 only (double-pass 46 rows; page footer claimed 47); female NPTF per ANSI B1.20.3; W@REF: OMi WebsitePartsInfo2026.xlsx Items!R1470 Hex Flat = 0.875 (table had 1.06) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; N1@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P1470 = 1.020 (table had 1.01) [user 2026-10-18 A19]; N1@DRIVE: Air-Way 1.01 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.02) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; W@REF: Air-Way 1.06 (raw 07_RAW_EXTRACTS; OMi file / Brennan 0.875) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); female legs: the forged hex arm stops 0.26 short of the port face and the end is a ROUND COLLAR of dia = the hex flats - MEASURED on the Brennan 2502-06-04-FG, 5502-04-04/-08-08/-16-16-FG, 5504-08-08-FG and 5605-08-08-08-FG STEPs (collar 0.260 at every size and leg; single manufacturer); port-mouth 45deg chamfer and hex chamfers not modelled; female NPTF legs: Air-Way tap drill to MS51503 P1 max (Brennan 5405-08-08 STEP: 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED -08 only)), tapered helix over P1; connecting drill to the axis crossing = the part's own D column (ASSUMPTION; capped at the tap drill where larger); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>A19 (user 2026-10-18, group 3 open): N1@DRIVE 1.01 -&gt; OMi 1.020 (Items!P1470, M110)</t>
+          <t>A19 (user 2026-10-18, group 3 open): N1@DRIVE 1.01 -&gt; OMi 1.020 (Items!P1470, M110) | 2026-10-20 Air-Way first: N1@DRIVE OMi/Brennan 1.02 -&gt; Air-Way 1.01 | 2026-10-20 Air-Way first: W@REF OMi/Brennan 0.875 -&gt; Air-Way 1.06</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -2841,7 +2846,7 @@
         <v>1.97</v>
       </c>
       <c r="C16" t="n">
-        <v>0.656</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="D16" t="n">
         <v>0.6415999999999999</v>
@@ -2856,10 +2861,10 @@
         <v>0.2572</v>
       </c>
       <c r="H16" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="I16" t="n">
-        <v>0.656</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="J16" t="n">
         <v>0.9399999999999999</v>
@@ -2877,7 +2882,7 @@
         <v>0.91</v>
       </c>
       <c r="O16" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="P16" t="n">
         <v>1.2832</v>
@@ -2913,34 +2918,34 @@
         <v>0.51214</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.312</v>
+        <v>1.63</v>
       </c>
       <c r="AC16" t="n">
         <v>1.03</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.312</v>
+        <v>1.63</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.656</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.656</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="AH16" t="n">
-        <v>0.37824</v>
+        <v>0.47004</v>
       </c>
       <c r="AI16" t="n">
-        <v>0.37824</v>
+        <v>0.47004</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.75698</v>
+        <v>0.94058</v>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
@@ -2974,12 +2979,12 @@
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>Air-Way s128 only (double-pass 46 rows; page footer claimed 47); female NPTF per ANSI B1.20.3 | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); female legs: the forged hex arm stops 0.26 short of the port face and the end is a ROUND COLLAR of dia = the hex flats - MEASURED on the Brennan 2502-06-04-FG, 5502-04-04/-08-08/-16-16-FG, 5504-08-08-FG and 5605-08-08-08-FG STEPs (collar 0.260 at every size and leg; single manufacturer); port-mouth 45deg chamfer and hex chamfers not modelled; female NPTF legs: Air-Way tap drill to MS51503 P1 max (Brennan 5405-08-08 STEP: 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED -08 only)), tapered helix over P1; connecting drill to the axis crossing = the part's own D column (ASSUMPTION; capped at the tap drill where larger); each leg bore runs from its face to the axis crossing</t>
+          <t>Air-Way s128 only (double-pass 46 rows; page footer claimed 47); female NPTF per ANSI B1.20.3; N1@DRIVE: Air-Way 1.39 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.36) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; W@REF: Air-Way 1.63 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.312) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); female legs: the forged hex arm stops 0.26 short of the port face and the end is a ROUND COLLAR of dia = the hex flats - MEASURED on the Brennan 2502-06-04-FG, 5502-04-04/-08-08/-16-16-FG, 5504-08-08-FG and 5605-08-08-08-FG STEPs (collar 0.260 at every size and leg; single manufacturer); port-mouth 45deg chamfer and hex chamfers not modelled; female NPTF legs: Air-Way tap drill to MS51503 P1 max (Brennan 5405-08-08 STEP: 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED -08 only)), tapered helix over P1; connecting drill to the axis crossing = the part's own D column (ASSUMPTION; capped at the tap drill where larger); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>DROP: no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-16: BUILD - the DROP above is void: OMi sells this part, the 2026-09-23 crawl had dropped its SKU | OMi dims first (user 2026-09-25): W@REF: OMi WebsitePartsInfo2026.xlsx Items!R1477 = 1.312 (table had 1.63) | Brennan TFA TFA-p031-t03: agrees on N@DRIVE, W@REF, D@BORE; DIFFERS on N1@DRIVE 1.39 vs Brennan N1 LGTH 1.360 (built to the dimension source, s6) | A19-style (user 2026-10-18 'yes, apply the 7 pending OMi values'): N1@DRIVE 1.39 -&gt; 1.36 | leg 1: male NPTF thread dia at L2 1.3259 vs hex flats 1.3120 (round end proud of the flats by 0.0069; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012)</t>
+          <t>DROP: no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-16: BUILD - the DROP above is void: OMi sells this part, the 2026-09-23 crawl had dropped its SKU | OMi dims first (user 2026-09-25): W@REF: OMi WebsitePartsInfo2026.xlsx Items!R1477 = 1.312 (table had 1.63) | Brennan TFA TFA-p031-t03: agrees on N@DRIVE, W@REF, D@BORE; DIFFERS on N1@DRIVE 1.39 vs Brennan N1 LGTH 1.360 (built to the dimension source, s6) | A19-style (user 2026-10-18 'yes, apply the 7 pending OMi values'): N1@DRIVE 1.39 -&gt; 1.36 | 2026-10-20 Air-Way first: N1@DRIVE OMi/Brennan 1.36 -&gt; Air-Way 1.39 | 2026-10-20 Air-Way first: W@REF OMi/Brennan 1.312 -&gt; Air-Way 1.63</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -3309,7 +3314,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="C19" t="n">
         <v>0.9399999999999999</v>
@@ -3336,7 +3341,7 @@
         <v>1.25</v>
       </c>
       <c r="K19" t="n">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="L19" t="n">
         <v>1.48</v>
@@ -3366,7 +3371,7 @@
         <v>0.74378</v>
       </c>
       <c r="U19" t="n">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="V19" t="n">
         <v>1.48</v>
@@ -3390,7 +3395,7 @@
         <v>1.88</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.41</v>
+        <v>1.78</v>
       </c>
       <c r="AD19" t="n">
         <v>1.88</v>
@@ -3445,12 +3450,12 @@
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>Air-Way s128 only (double-pass 46 rows; page footer claimed 47); female NPTF per ANSI B1.20.3; N@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!N1481 = 2.380 (table had 2.75) [user 2026-10-18 A19] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); female legs: the forged hex arm stops 0.26 short of the port face and the end is a ROUND COLLAR of dia = the hex flats - MEASURED on the Brennan 2502-06-04-FG, 5502-04-04/-08-08/-16-16-FG, 5504-08-08-FG and 5605-08-08-08-FG STEPs (collar 0.260 at every size and leg; single manufacturer); port-mouth 45deg chamfer and hex chamfers not modelled; female NPTF legs: Air-Way tap drill to MS51503 P1 max (Brennan 5405-08-08 STEP: 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED -08 only)), tapered helix over P1; connecting drill to the axis crossing = the part's own D column (ASSUMPTION; capped at the tap drill where larger); each leg bore runs from its face to the axis crossing</t>
+          <t>Air-Way s128 only (double-pass 46 rows; page footer claimed 47); female NPTF per ANSI B1.20.3; N@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!N1481 = 2.380 (table had 2.75) [user 2026-10-18 A19]; N@DRIVE: Air-Way 2.75 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.38) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); female legs: the forged hex arm stops 0.26 short of the port face and the end is a ROUND COLLAR of dia = the hex flats - MEASURED on the Brennan 2502-06-04-FG, 5502-04-04/-08-08/-16-16-FG, 5504-08-08-FG and 5605-08-08-08-FG STEPs (collar 0.260 at every size and leg; single manufacturer); port-mouth 45deg chamfer and hex chamfers not modelled; female NPTF legs: Air-Way tap drill to MS51503 P1 max (Brennan 5405-08-08 STEP: 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED -08 only)), tapered helix over P1; connecting drill to the axis crossing = the part's own D column (ASSUMPTION; capped at the tap drill where larger); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>N 2.75 vs non-FG 2.38 (FG &gt; non-FG by .37, unusual) - as-printed | A19 (user 2026-10-18, group 3 open): N@DRIVE 2.75 -&gt; OMi 2.380 (Items!N1481, M109)</t>
+          <t>N 2.75 vs non-FG 2.38 (FG &gt; non-FG by .37, unusual) - as-printed | A19 (user 2026-10-18, group 3 open): N@DRIVE 2.75 -&gt; OMi 2.380 (Items!N1481, M109) | 2026-10-20 Air-Way first: N@DRIVE OMi/Brennan 2.38 -&gt; Air-Way 2.75</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -3466,7 +3471,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.64</v>
+        <v>3.05</v>
       </c>
       <c r="C20" t="n">
         <v>1.28</v>
@@ -3493,7 +3498,7 @@
         <v>1.5</v>
       </c>
       <c r="K20" t="n">
-        <v>2.64</v>
+        <v>3.05</v>
       </c>
       <c r="L20" t="n">
         <v>1.72</v>
@@ -3523,7 +3528,7 @@
         <v>0.86326</v>
       </c>
       <c r="U20" t="n">
-        <v>2.64</v>
+        <v>3.05</v>
       </c>
       <c r="V20" t="n">
         <v>1.72</v>
@@ -3547,7 +3552,7 @@
         <v>2.56</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.64</v>
+        <v>2.05</v>
       </c>
       <c r="AD20" t="n">
         <v>2.56</v>
@@ -3602,12 +3607,12 @@
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>Air-Way s128 only (double-pass 46 rows; page footer claimed 47); female NPTF per ANSI B1.20.3; N@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!N1484 = 2.640 (table had 3.05) [user 2026-10-18 A19] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); female legs: the forged hex arm stops 0.26 short of the port face and the end is a ROUND COLLAR of dia = the hex flats - MEASURED on the Brennan 2502-06-04-FG, 5502-04-04/-08-08/-16-16-FG, 5504-08-08-FG and 5605-08-08-08-FG STEPs (collar 0.260 at every size and leg; single manufacturer); port-mouth 45deg chamfer and hex chamfers not modelled; female NPTF legs: Air-Way tap drill to MS51503 P1 max (Brennan 5405-08-08 STEP: 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED -08 only)), tapered helix over P1; connecting drill to the axis crossing = the part's own D column (ASSUMPTION; capped at the tap drill where larger); each leg bore runs from its face to the axis crossing</t>
+          <t>Air-Way s128 only (double-pass 46 rows; page footer claimed 47); female NPTF per ANSI B1.20.3; N@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!N1484 = 2.640 (table had 3.05) [user 2026-10-18 A19]; N@DRIVE: Air-Way 3.05 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.64) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); female legs: the forged hex arm stops 0.26 short of the port face and the end is a ROUND COLLAR of dia = the hex flats - MEASURED on the Brennan 2502-06-04-FG, 5502-04-04/-08-08/-16-16-FG, 5504-08-08-FG and 5605-08-08-08-FG STEPs (collar 0.260 at every size and leg; single manufacturer); port-mouth 45deg chamfer and hex chamfers not modelled; female NPTF legs: Air-Way tap drill to MS51503 P1 max (Brennan 5405-08-08 STEP: 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED -08 only)), tapered helix over P1; connecting drill to the axis crossing = the part's own D column (ASSUMPTION; capped at the tap drill where larger); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>N 3.05 vs non-FG 2.70 - as-printed | A19 (user 2026-10-18, group 3 open): N@DRIVE 3.05 -&gt; OMi 2.640 (Items!N1484, M109)</t>
+          <t>N 3.05 vs non-FG 2.70 - as-printed | A19 (user 2026-10-18, group 3 open): N@DRIVE 3.05 -&gt; OMi 2.640 (Items!N1484, M109) | 2026-10-20 Air-Way first: N@DRIVE OMi/Brennan 2.64 -&gt; Air-Way 3.05</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
